--- a/Game Components Assets/Jutland Gun ResolveV1.xlsx
+++ b/Game Components Assets/Jutland Gun ResolveV1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12960" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="损伤表" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,10 @@
     <sheet name="甲弹表" sheetId="3" r:id="rId4"/>
     <sheet name="中口径结算表" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">损伤表!$A$1:$Z$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'命中表 '!$A$1:$R$33</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="230">
   <si>
     <r>
       <rPr>
@@ -432,7 +436,7 @@
         <vertAlign val="subscript"/>
         <sz val="14"/>
         <color theme="0"/>
-        <rFont val="宋体"/>
+        <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
       <t>命中率</t>
@@ -442,7 +446,7 @@
         <vertAlign val="superscript"/>
         <sz val="14"/>
         <color theme="0"/>
-        <rFont val="宋体"/>
+        <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">    射击数</t>
@@ -578,16 +582,29 @@
     <t>-5%</t>
   </si>
   <si>
+    <t>对低速（&lt;=10kn）目标射击,
+x=CEILING[(11-Speed)/2]</t>
+  </si>
+  <si>
+    <t>+x%</t>
+  </si>
+  <si>
     <t>烟雾射击（英）</t>
   </si>
   <si>
     <t>烟雾射击（德）</t>
   </si>
   <si>
-    <t>黑夜射击(英）</t>
-  </si>
-  <si>
-    <t>黑夜射击（德）</t>
+    <t>夜间射击(英）</t>
+  </si>
+  <si>
+    <t>/2.5</t>
+  </si>
+  <si>
+    <t>夜间射击（德）</t>
+  </si>
+  <si>
+    <t>/2</t>
   </si>
   <si>
     <t>命中率不低于0%</t>
@@ -606,6 +623,9 @@
   </si>
   <si>
     <t>疲劳：德舰开火累计2h后触发</t>
+  </si>
+  <si>
+    <t>优火控：QE class &amp; R class</t>
   </si>
   <si>
     <r>
@@ -1262,7 +1282,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="53">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1364,19 +1384,13 @@
       <vertAlign val="subscript"/>
       <sz val="14"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="0"/>
       <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1613,16 +1627,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <vertAlign val="superscript"/>
-      <sz val="14"/>
-      <color theme="0"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <vertAlign val="superscript"/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="黑体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1976,7 +1990,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -2023,132 +2037,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="4"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4"/>
-      </right>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4"/>
-      </right>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="4"/>
-      </left>
-      <right/>
-      <top style="double">
-        <color theme="4"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalDown="1">
-      <left style="thin">
-        <color theme="4"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal style="thin">
-        <color auto="1"/>
-      </diagonal>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4" tint="0.399975585192419"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="4"/>
-      </right>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="thin">
-        <color theme="4" tint="0.399975585192419"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
@@ -2174,6 +2062,32 @@
         <color auto="1"/>
       </left>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -2192,17 +2106,67 @@
         <color auto="1"/>
       </left>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top/>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color theme="4"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right style="thin">
         <color auto="1"/>
+      </right>
+      <top style="double">
+        <color theme="4"/>
       </top>
       <bottom style="thin">
         <color auto="1"/>
@@ -2235,8 +2199,151 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalDown="1">
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.399975585192419"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -2249,6 +2356,26 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="thin">
         <color auto="1"/>
@@ -2373,137 +2500,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="33" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="34" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="35" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="29" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="29" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="30" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="30" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="30" borderId="36" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="30" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="31" borderId="38" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="31" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="221">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2636,172 +2763,241 @@
     <xf numFmtId="9" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="13" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="14" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="14" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="14" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="14" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="14" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="14" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2810,22 +3006,22 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
@@ -2834,227 +3030,269 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="18" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="21" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="21" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="23" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3377,2476 +3615,2478 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AF61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="26" style="60" customWidth="1"/>
-    <col min="2" max="2" width="18.875" style="60" customWidth="1"/>
-    <col min="3" max="6" width="6.375" style="60" customWidth="1"/>
-    <col min="7" max="26" width="3.33333333333333" style="60" customWidth="1"/>
-    <col min="27" max="27" width="9" style="60"/>
-    <col min="28" max="28" width="10.625" style="60" customWidth="1"/>
-    <col min="29" max="29" width="15.625" style="60" customWidth="1"/>
-    <col min="30" max="30" width="9" style="60"/>
-    <col min="31" max="31" width="10.625" style="60" customWidth="1"/>
-    <col min="32" max="32" width="15.625" style="60" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="60"/>
+    <col min="1" max="1" width="26" style="83" customWidth="1"/>
+    <col min="2" max="2" width="18.875" style="83" customWidth="1"/>
+    <col min="3" max="6" width="6.375" style="83" customWidth="1"/>
+    <col min="7" max="26" width="3.33333333333333" style="83" customWidth="1"/>
+    <col min="27" max="27" width="9" style="83"/>
+    <col min="28" max="28" width="10.625" style="83" customWidth="1"/>
+    <col min="29" max="29" width="15.625" style="83" customWidth="1"/>
+    <col min="30" max="30" width="9" style="83"/>
+    <col min="31" max="31" width="10.625" style="83" customWidth="1"/>
+    <col min="32" max="32" width="15.625" style="83" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="83"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:32">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="66" t="s">
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="67"/>
-      <c r="I1" s="128" t="s">
+      <c r="H1" s="90"/>
+      <c r="I1" s="157" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="129" t="s">
+      <c r="J1" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="130"/>
-      <c r="L1" s="130"/>
-      <c r="M1" s="130"/>
-      <c r="N1" s="130"/>
-      <c r="O1" s="130"/>
-      <c r="P1" s="130"/>
-      <c r="Q1" s="130"/>
-      <c r="R1" s="130"/>
-      <c r="S1" s="130"/>
-      <c r="T1" s="130"/>
-      <c r="U1" s="130"/>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="174"/>
-      <c r="AB1" s="175"/>
-      <c r="AC1" s="175"/>
-      <c r="AD1" s="175"/>
-      <c r="AE1" s="175"/>
-      <c r="AF1" s="175"/>
+      <c r="K1" s="159"/>
+      <c r="L1" s="159"/>
+      <c r="M1" s="159"/>
+      <c r="N1" s="159"/>
+      <c r="O1" s="159"/>
+      <c r="P1" s="159"/>
+      <c r="Q1" s="159"/>
+      <c r="R1" s="159"/>
+      <c r="S1" s="159"/>
+      <c r="T1" s="159"/>
+      <c r="U1" s="159"/>
+      <c r="V1" s="159"/>
+      <c r="W1" s="159"/>
+      <c r="X1" s="159"/>
+      <c r="Y1" s="159"/>
+      <c r="Z1" s="203"/>
+      <c r="AB1" s="204"/>
+      <c r="AC1" s="204"/>
+      <c r="AD1" s="204"/>
+      <c r="AE1" s="204"/>
+      <c r="AF1" s="204"/>
     </row>
     <row r="2" customHeight="1" spans="1:32">
-      <c r="A2" s="68"/>
-      <c r="B2" s="69"/>
-      <c r="C2" s="70" t="s">
+      <c r="A2" s="91"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="71" t="s">
+      <c r="D2" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="73">
+      <c r="G2" s="96">
         <v>1</v>
       </c>
-      <c r="H2" s="74">
+      <c r="H2" s="97">
         <v>2</v>
       </c>
-      <c r="I2" s="131">
+      <c r="I2" s="160">
         <v>3</v>
       </c>
-      <c r="J2" s="132">
+      <c r="J2" s="161">
         <v>4</v>
       </c>
-      <c r="K2" s="133">
+      <c r="K2" s="162">
         <v>5</v>
       </c>
-      <c r="L2" s="134">
+      <c r="L2" s="163">
         <v>6</v>
       </c>
-      <c r="M2" s="134">
+      <c r="M2" s="163">
         <v>7</v>
       </c>
-      <c r="N2" s="134">
+      <c r="N2" s="163">
         <v>8</v>
       </c>
-      <c r="O2" s="134">
+      <c r="O2" s="163">
         <v>9</v>
       </c>
-      <c r="P2" s="134">
+      <c r="P2" s="163">
         <v>10</v>
       </c>
-      <c r="Q2" s="134">
+      <c r="Q2" s="163">
         <v>11</v>
       </c>
-      <c r="R2" s="134">
+      <c r="R2" s="163">
         <v>12</v>
       </c>
-      <c r="S2" s="134">
+      <c r="S2" s="163">
         <v>13</v>
       </c>
-      <c r="T2" s="134">
+      <c r="T2" s="163">
         <v>14</v>
       </c>
-      <c r="U2" s="134">
+      <c r="U2" s="163">
         <v>15</v>
       </c>
-      <c r="V2" s="134">
+      <c r="V2" s="163">
         <v>16</v>
       </c>
-      <c r="W2" s="134">
+      <c r="W2" s="163">
         <v>17</v>
       </c>
-      <c r="X2" s="134">
+      <c r="X2" s="163">
         <v>18</v>
       </c>
-      <c r="Y2" s="134">
+      <c r="Y2" s="163">
         <v>19</v>
       </c>
-      <c r="Z2" s="176">
+      <c r="Z2" s="205">
         <v>20</v>
       </c>
-      <c r="AB2" s="175"/>
-      <c r="AC2" s="175"/>
-      <c r="AD2" s="175"/>
-      <c r="AE2" s="175"/>
-      <c r="AF2" s="175"/>
+      <c r="AB2" s="204"/>
+      <c r="AC2" s="204"/>
+      <c r="AD2" s="204"/>
+      <c r="AE2" s="204"/>
+      <c r="AF2" s="204"/>
     </row>
     <row r="3" customHeight="1" spans="1:32">
-      <c r="A3" s="75" t="s">
+      <c r="A3" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="77">
+      <c r="C3" s="100">
         <v>10500</v>
       </c>
-      <c r="D3" s="78">
+      <c r="D3" s="101">
         <v>15000</v>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="101">
         <v>18000</v>
       </c>
-      <c r="F3" s="79">
+      <c r="F3" s="102">
         <v>18500</v>
       </c>
-      <c r="G3" s="80">
+      <c r="G3" s="103">
         <v>1</v>
       </c>
-      <c r="H3" s="81">
+      <c r="H3" s="104">
         <v>2</v>
       </c>
-      <c r="I3" s="135"/>
-      <c r="J3" s="136">
+      <c r="I3" s="164"/>
+      <c r="J3" s="165">
         <v>6</v>
       </c>
-      <c r="K3" s="137"/>
-      <c r="L3" s="138">
+      <c r="K3" s="166"/>
+      <c r="L3" s="167">
         <v>3</v>
       </c>
-      <c r="M3" s="135">
+      <c r="M3" s="164">
         <v>5</v>
       </c>
-      <c r="N3" s="135">
+      <c r="N3" s="164">
         <v>5</v>
       </c>
-      <c r="O3" s="139">
+      <c r="O3" s="168">
         <v>4</v>
       </c>
-      <c r="P3" s="140">
+      <c r="P3" s="169">
         <v>5</v>
       </c>
-      <c r="Q3" s="172">
+      <c r="Q3" s="201">
         <v>5</v>
       </c>
-      <c r="R3" s="137"/>
-      <c r="S3" s="138">
+      <c r="R3" s="166"/>
+      <c r="S3" s="167">
         <v>2</v>
       </c>
-      <c r="T3" s="135">
+      <c r="T3" s="164">
         <v>3</v>
       </c>
-      <c r="U3" s="135">
+      <c r="U3" s="164">
         <v>2</v>
       </c>
-      <c r="V3" s="135" t="s">
+      <c r="V3" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="W3" s="135" t="s">
+      <c r="W3" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="X3" s="135" t="s">
+      <c r="X3" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="Y3" s="135" t="s">
+      <c r="Y3" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="Z3" s="177" t="s">
+      <c r="Z3" s="206" t="s">
         <v>12</v>
       </c>
-      <c r="AB3" s="178"/>
-      <c r="AC3" s="178"/>
-      <c r="AD3" s="179"/>
-      <c r="AE3" s="178"/>
-      <c r="AF3" s="178"/>
+      <c r="AB3" s="207"/>
+      <c r="AC3" s="207"/>
+      <c r="AD3" s="208"/>
+      <c r="AE3" s="207"/>
+      <c r="AF3" s="207"/>
     </row>
     <row r="4" customHeight="1" spans="1:32">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="84">
+      <c r="C4" s="107">
         <v>10500</v>
       </c>
-      <c r="D4" s="85">
+      <c r="D4" s="108">
         <v>15000</v>
       </c>
-      <c r="E4" s="85">
+      <c r="E4" s="108">
         <v>18000</v>
       </c>
-      <c r="F4" s="86">
+      <c r="F4" s="109">
         <v>18500</v>
       </c>
-      <c r="G4" s="87">
+      <c r="G4" s="110">
         <v>1</v>
       </c>
-      <c r="H4" s="88">
+      <c r="H4" s="111">
         <v>2</v>
       </c>
-      <c r="I4" s="92"/>
-      <c r="J4" s="141">
+      <c r="I4" s="115"/>
+      <c r="J4" s="170">
         <v>6</v>
       </c>
-      <c r="K4" s="142"/>
-      <c r="L4" s="143">
+      <c r="K4" s="171"/>
+      <c r="L4" s="172">
         <v>3</v>
       </c>
-      <c r="M4" s="92">
+      <c r="M4" s="115">
         <v>5</v>
       </c>
-      <c r="N4" s="92">
+      <c r="N4" s="115">
         <v>5</v>
       </c>
-      <c r="O4" s="144">
+      <c r="O4" s="173">
         <v>4</v>
       </c>
-      <c r="P4" s="145">
+      <c r="P4" s="174">
         <v>5</v>
       </c>
-      <c r="Q4" s="147">
+      <c r="Q4" s="176">
         <v>5</v>
       </c>
-      <c r="R4" s="142"/>
-      <c r="S4" s="143">
+      <c r="R4" s="171"/>
+      <c r="S4" s="172">
         <v>2</v>
       </c>
-      <c r="T4" s="92">
+      <c r="T4" s="115">
         <v>3</v>
       </c>
-      <c r="U4" s="92">
+      <c r="U4" s="115">
         <v>2</v>
       </c>
-      <c r="V4" s="87" t="s">
+      <c r="V4" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="W4" s="92" t="s">
+      <c r="W4" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="X4" s="92" t="s">
+      <c r="X4" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Y4" s="92" t="s">
+      <c r="Y4" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="180" t="s">
+      <c r="Z4" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="AB4" s="178"/>
-      <c r="AC4" s="178"/>
-      <c r="AD4" s="179"/>
-      <c r="AE4" s="178"/>
-      <c r="AF4" s="178"/>
+      <c r="AB4" s="207"/>
+      <c r="AC4" s="207"/>
+      <c r="AD4" s="208"/>
+      <c r="AE4" s="207"/>
+      <c r="AF4" s="207"/>
     </row>
     <row r="5" customHeight="1" spans="1:32">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="84">
+      <c r="C5" s="107">
         <v>13500</v>
       </c>
-      <c r="D5" s="85">
+      <c r="D5" s="108">
         <v>19500</v>
       </c>
-      <c r="E5" s="85">
+      <c r="E5" s="108">
         <v>21000</v>
       </c>
-      <c r="F5" s="89"/>
-      <c r="G5" s="87">
+      <c r="F5" s="112"/>
+      <c r="G5" s="110">
         <v>1</v>
       </c>
-      <c r="H5" s="88">
+      <c r="H5" s="111">
         <v>2</v>
       </c>
-      <c r="I5" s="92"/>
-      <c r="J5" s="141">
+      <c r="I5" s="115"/>
+      <c r="J5" s="170">
         <v>6</v>
       </c>
-      <c r="K5" s="142"/>
-      <c r="L5" s="143">
+      <c r="K5" s="171"/>
+      <c r="L5" s="172">
         <v>3</v>
       </c>
-      <c r="M5" s="92">
+      <c r="M5" s="115">
         <v>5</v>
       </c>
-      <c r="N5" s="92">
+      <c r="N5" s="115">
         <v>5</v>
       </c>
-      <c r="O5" s="144">
+      <c r="O5" s="173">
         <v>4</v>
       </c>
-      <c r="P5" s="145">
+      <c r="P5" s="174">
         <v>5</v>
       </c>
-      <c r="Q5" s="147">
+      <c r="Q5" s="176">
         <v>5</v>
       </c>
-      <c r="R5" s="142"/>
-      <c r="S5" s="143">
+      <c r="R5" s="171"/>
+      <c r="S5" s="172">
         <v>3</v>
       </c>
-      <c r="T5" s="92">
+      <c r="T5" s="115">
         <v>4</v>
       </c>
-      <c r="U5" s="92">
+      <c r="U5" s="115">
         <v>4</v>
       </c>
-      <c r="V5" s="87" t="s">
+      <c r="V5" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="W5" s="92" t="s">
+      <c r="W5" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="X5" s="92" t="s">
+      <c r="X5" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Y5" s="92" t="s">
+      <c r="Y5" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Z5" s="180" t="s">
+      <c r="Z5" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="AB5" s="178"/>
-      <c r="AC5" s="178"/>
-      <c r="AD5" s="179"/>
-      <c r="AE5" s="178"/>
-      <c r="AF5" s="178"/>
+      <c r="AB5" s="207"/>
+      <c r="AC5" s="207"/>
+      <c r="AD5" s="208"/>
+      <c r="AE5" s="207"/>
+      <c r="AF5" s="207"/>
     </row>
     <row r="6" customHeight="1" spans="1:32">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="84">
+      <c r="C6" s="107">
         <v>13000</v>
       </c>
-      <c r="D6" s="85">
+      <c r="D6" s="108">
         <v>19500</v>
       </c>
-      <c r="E6" s="85">
+      <c r="E6" s="108">
         <v>23500</v>
       </c>
-      <c r="F6" s="89"/>
-      <c r="G6" s="87">
+      <c r="F6" s="112"/>
+      <c r="G6" s="110">
         <v>2</v>
       </c>
-      <c r="H6" s="88">
+      <c r="H6" s="111">
         <v>4</v>
       </c>
-      <c r="I6" s="92"/>
-      <c r="J6" s="146">
+      <c r="I6" s="115"/>
+      <c r="J6" s="175">
         <v>9</v>
       </c>
-      <c r="K6" s="147">
+      <c r="K6" s="176">
         <v>9</v>
       </c>
-      <c r="L6" s="142"/>
-      <c r="M6" s="143">
+      <c r="L6" s="171"/>
+      <c r="M6" s="172">
         <v>5</v>
       </c>
-      <c r="N6" s="92">
+      <c r="N6" s="115">
         <v>8</v>
       </c>
-      <c r="O6" s="92">
+      <c r="O6" s="115">
         <v>8</v>
       </c>
-      <c r="P6" s="144">
+      <c r="P6" s="173">
         <v>7</v>
       </c>
-      <c r="Q6" s="145">
+      <c r="Q6" s="174">
         <v>8</v>
       </c>
-      <c r="R6" s="147">
+      <c r="R6" s="176">
         <v>8</v>
       </c>
-      <c r="S6" s="142"/>
-      <c r="T6" s="143">
+      <c r="S6" s="171"/>
+      <c r="T6" s="172">
         <v>4</v>
       </c>
-      <c r="U6" s="92">
+      <c r="U6" s="115">
         <v>7</v>
       </c>
-      <c r="V6" s="92">
+      <c r="V6" s="115">
         <v>7</v>
       </c>
-      <c r="W6" s="92" t="s">
+      <c r="W6" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="X6" s="92" t="s">
+      <c r="X6" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Y6" s="92" t="s">
+      <c r="Y6" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Z6" s="180" t="s">
+      <c r="Z6" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="AB6" s="178"/>
-      <c r="AC6" s="178"/>
-      <c r="AD6" s="179"/>
-      <c r="AE6" s="178"/>
-      <c r="AF6" s="178"/>
+      <c r="AB6" s="207"/>
+      <c r="AC6" s="207"/>
+      <c r="AD6" s="208"/>
+      <c r="AE6" s="207"/>
+      <c r="AF6" s="207"/>
     </row>
     <row r="7" customHeight="1" spans="1:32">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="84">
+      <c r="C7" s="107">
         <v>13000</v>
       </c>
-      <c r="D7" s="85">
+      <c r="D7" s="108">
         <v>19500</v>
       </c>
-      <c r="E7" s="85">
+      <c r="E7" s="108">
         <v>23500</v>
       </c>
-      <c r="F7" s="89"/>
-      <c r="G7" s="87">
+      <c r="F7" s="112"/>
+      <c r="G7" s="110">
         <v>2</v>
       </c>
-      <c r="H7" s="88">
+      <c r="H7" s="111">
         <v>4</v>
       </c>
-      <c r="I7" s="92"/>
-      <c r="J7" s="146">
+      <c r="I7" s="115"/>
+      <c r="J7" s="175">
         <v>9</v>
       </c>
-      <c r="K7" s="147">
+      <c r="K7" s="176">
         <v>9</v>
       </c>
-      <c r="L7" s="142"/>
-      <c r="M7" s="143">
+      <c r="L7" s="171"/>
+      <c r="M7" s="172">
         <v>5</v>
       </c>
-      <c r="N7" s="92">
+      <c r="N7" s="115">
         <v>8</v>
       </c>
-      <c r="O7" s="92">
+      <c r="O7" s="115">
         <v>8</v>
       </c>
-      <c r="P7" s="144">
+      <c r="P7" s="173">
         <v>7</v>
       </c>
-      <c r="Q7" s="145">
+      <c r="Q7" s="174">
         <v>8</v>
       </c>
-      <c r="R7" s="147">
+      <c r="R7" s="176">
         <v>8</v>
       </c>
-      <c r="S7" s="142"/>
-      <c r="T7" s="143">
+      <c r="S7" s="171"/>
+      <c r="T7" s="172">
         <v>4</v>
       </c>
-      <c r="U7" s="92">
+      <c r="U7" s="115">
         <v>7</v>
       </c>
-      <c r="V7" s="92">
+      <c r="V7" s="115">
         <v>7</v>
       </c>
-      <c r="W7" s="92">
+      <c r="W7" s="115">
         <v>5</v>
       </c>
-      <c r="X7" s="92" t="s">
+      <c r="X7" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Y7" s="92" t="s">
+      <c r="Y7" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Z7" s="180" t="s">
+      <c r="Z7" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="AB7" s="178"/>
-      <c r="AC7" s="178"/>
-      <c r="AD7" s="179"/>
-      <c r="AE7" s="178"/>
-      <c r="AF7" s="178"/>
+      <c r="AB7" s="207"/>
+      <c r="AC7" s="207"/>
+      <c r="AD7" s="208"/>
+      <c r="AE7" s="207"/>
+      <c r="AF7" s="207"/>
     </row>
     <row r="8" customHeight="1" spans="1:32">
-      <c r="A8" s="82" t="s">
+      <c r="A8" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="84">
+      <c r="C8" s="107">
         <v>12000</v>
       </c>
-      <c r="D8" s="85">
+      <c r="D8" s="108">
         <v>18500</v>
       </c>
-      <c r="E8" s="85">
+      <c r="E8" s="108">
         <v>24000</v>
       </c>
-      <c r="F8" s="86">
+      <c r="F8" s="109">
         <v>24500</v>
       </c>
-      <c r="G8" s="87">
+      <c r="G8" s="110">
         <v>3</v>
       </c>
-      <c r="H8" s="88">
+      <c r="H8" s="111">
         <v>5</v>
       </c>
-      <c r="I8" s="92"/>
-      <c r="J8" s="148">
+      <c r="I8" s="115"/>
+      <c r="J8" s="177">
         <v>10</v>
       </c>
-      <c r="K8" s="145">
+      <c r="K8" s="174">
         <v>12</v>
       </c>
-      <c r="L8" s="147">
+      <c r="L8" s="176">
         <v>12</v>
       </c>
-      <c r="M8" s="142"/>
-      <c r="N8" s="143">
+      <c r="M8" s="171"/>
+      <c r="N8" s="172">
         <v>6</v>
       </c>
-      <c r="O8" s="92">
+      <c r="O8" s="115">
         <v>10</v>
       </c>
-      <c r="P8" s="92">
+      <c r="P8" s="115">
         <v>10</v>
       </c>
-      <c r="Q8" s="144">
+      <c r="Q8" s="173">
         <v>10</v>
       </c>
-      <c r="R8" s="145">
+      <c r="R8" s="174">
         <v>11</v>
       </c>
-      <c r="S8" s="147">
+      <c r="S8" s="176">
         <v>11</v>
       </c>
-      <c r="T8" s="142"/>
-      <c r="U8" s="143">
+      <c r="T8" s="171"/>
+      <c r="U8" s="172">
         <v>6</v>
       </c>
-      <c r="V8" s="92">
+      <c r="V8" s="115">
         <v>9</v>
       </c>
-      <c r="W8" s="92">
+      <c r="W8" s="115">
         <v>9</v>
       </c>
-      <c r="X8" s="92" t="s">
+      <c r="X8" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Y8" s="92" t="s">
+      <c r="Y8" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Z8" s="180" t="s">
+      <c r="Z8" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="AB8" s="178"/>
-      <c r="AC8" s="178"/>
-      <c r="AD8" s="179"/>
-      <c r="AE8" s="178"/>
-      <c r="AF8" s="178"/>
+      <c r="AB8" s="207"/>
+      <c r="AC8" s="207"/>
+      <c r="AD8" s="208"/>
+      <c r="AE8" s="207"/>
+      <c r="AF8" s="207"/>
     </row>
     <row r="9" customHeight="1" spans="1:32">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="84">
+      <c r="C9" s="107">
         <v>12000</v>
       </c>
-      <c r="D9" s="85">
+      <c r="D9" s="108">
         <v>18500</v>
       </c>
-      <c r="E9" s="85">
+      <c r="E9" s="108">
         <v>23500</v>
       </c>
-      <c r="F9" s="89"/>
-      <c r="G9" s="92">
+      <c r="F9" s="112"/>
+      <c r="G9" s="115">
         <v>3</v>
       </c>
-      <c r="H9" s="88">
+      <c r="H9" s="111">
         <v>5</v>
       </c>
-      <c r="I9" s="92"/>
-      <c r="J9" s="148">
+      <c r="I9" s="115"/>
+      <c r="J9" s="177">
         <v>10</v>
       </c>
-      <c r="K9" s="145">
+      <c r="K9" s="174">
         <v>12</v>
       </c>
-      <c r="L9" s="147">
+      <c r="L9" s="176">
         <v>12</v>
       </c>
-      <c r="M9" s="142"/>
-      <c r="N9" s="143">
+      <c r="M9" s="171"/>
+      <c r="N9" s="172">
         <v>6</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="115">
         <v>10</v>
       </c>
-      <c r="P9" s="92">
+      <c r="P9" s="115">
         <v>10</v>
       </c>
-      <c r="Q9" s="144">
+      <c r="Q9" s="173">
         <v>10</v>
       </c>
-      <c r="R9" s="145">
+      <c r="R9" s="174">
         <v>11</v>
       </c>
-      <c r="S9" s="147">
+      <c r="S9" s="176">
         <v>11</v>
       </c>
-      <c r="T9" s="142"/>
-      <c r="U9" s="143">
+      <c r="T9" s="171"/>
+      <c r="U9" s="172">
         <v>6</v>
       </c>
-      <c r="V9" s="92">
+      <c r="V9" s="115">
         <v>9</v>
       </c>
-      <c r="W9" s="92">
+      <c r="W9" s="115">
         <v>9</v>
       </c>
-      <c r="X9" s="92">
+      <c r="X9" s="115">
         <v>7</v>
       </c>
-      <c r="Y9" s="92" t="s">
+      <c r="Y9" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Z9" s="180" t="s">
+      <c r="Z9" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="AB9" s="178"/>
-      <c r="AC9" s="178"/>
-      <c r="AD9" s="179"/>
-      <c r="AE9" s="179"/>
-      <c r="AF9" s="179"/>
+      <c r="AB9" s="207"/>
+      <c r="AC9" s="207"/>
+      <c r="AD9" s="208"/>
+      <c r="AE9" s="208"/>
+      <c r="AF9" s="208"/>
     </row>
     <row r="10" customHeight="1" spans="1:32">
-      <c r="A10" s="82"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="94" t="s">
+      <c r="A10" s="105"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="95" t="s">
+      <c r="D10" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="95" t="s">
+      <c r="E10" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="96" t="s">
+      <c r="F10" s="119" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="97">
+      <c r="G10" s="120">
         <v>1</v>
       </c>
-      <c r="H10" s="98">
+      <c r="H10" s="121">
         <v>2</v>
       </c>
-      <c r="I10" s="149">
+      <c r="I10" s="178">
         <v>3</v>
       </c>
-      <c r="J10" s="150">
+      <c r="J10" s="179">
         <v>4</v>
       </c>
-      <c r="K10" s="151">
+      <c r="K10" s="180">
         <v>5</v>
       </c>
-      <c r="L10" s="151">
+      <c r="L10" s="180">
         <v>6</v>
       </c>
-      <c r="M10" s="151">
+      <c r="M10" s="180">
         <v>7</v>
       </c>
-      <c r="N10" s="151">
+      <c r="N10" s="180">
         <v>8</v>
       </c>
-      <c r="O10" s="151">
+      <c r="O10" s="180">
         <v>9</v>
       </c>
-      <c r="P10" s="151">
+      <c r="P10" s="180">
         <v>10</v>
       </c>
-      <c r="Q10" s="151">
+      <c r="Q10" s="180">
         <v>11</v>
       </c>
-      <c r="R10" s="151">
+      <c r="R10" s="180">
         <v>12</v>
       </c>
-      <c r="S10" s="151">
+      <c r="S10" s="180">
         <v>13</v>
       </c>
-      <c r="T10" s="151">
+      <c r="T10" s="180">
         <v>14</v>
       </c>
-      <c r="U10" s="151">
+      <c r="U10" s="180">
         <v>15</v>
       </c>
-      <c r="V10" s="151">
+      <c r="V10" s="180">
         <v>16</v>
       </c>
-      <c r="W10" s="151">
+      <c r="W10" s="180">
         <v>17</v>
       </c>
-      <c r="X10" s="151">
+      <c r="X10" s="180">
         <v>18</v>
       </c>
-      <c r="Y10" s="151">
+      <c r="Y10" s="180">
         <v>19</v>
       </c>
-      <c r="Z10" s="181">
+      <c r="Z10" s="210">
         <v>20</v>
       </c>
-      <c r="AB10" s="178"/>
-      <c r="AC10" s="178"/>
-      <c r="AD10" s="179"/>
-      <c r="AE10" s="179"/>
-      <c r="AF10" s="179"/>
+      <c r="AB10" s="207"/>
+      <c r="AC10" s="207"/>
+      <c r="AD10" s="208"/>
+      <c r="AE10" s="208"/>
+      <c r="AF10" s="208"/>
     </row>
     <row r="11" customHeight="1" spans="1:32">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="99">
+      <c r="C11" s="122">
         <v>12000</v>
       </c>
-      <c r="D11" s="100">
+      <c r="D11" s="123">
         <v>17000</v>
       </c>
-      <c r="E11" s="100">
+      <c r="E11" s="123">
         <v>21000</v>
       </c>
-      <c r="F11" s="89">
+      <c r="F11" s="112">
         <v>22000</v>
       </c>
-      <c r="G11" s="92" t="s">
+      <c r="G11" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="88">
+      <c r="H11" s="111">
         <v>1</v>
       </c>
-      <c r="I11" s="92"/>
-      <c r="J11" s="141">
+      <c r="I11" s="115"/>
+      <c r="J11" s="170">
         <v>4</v>
       </c>
-      <c r="K11" s="142"/>
-      <c r="L11" s="143">
+      <c r="K11" s="171"/>
+      <c r="L11" s="172">
         <v>2</v>
       </c>
-      <c r="M11" s="92">
+      <c r="M11" s="115">
         <v>3</v>
       </c>
-      <c r="N11" s="92">
+      <c r="N11" s="115">
         <v>3</v>
       </c>
-      <c r="O11" s="144">
+      <c r="O11" s="173">
         <v>2</v>
       </c>
-      <c r="P11" s="145">
+      <c r="P11" s="174">
         <v>3</v>
       </c>
-      <c r="Q11" s="147">
+      <c r="Q11" s="176">
         <v>3</v>
       </c>
-      <c r="R11" s="142"/>
-      <c r="S11" s="143">
+      <c r="R11" s="171"/>
+      <c r="S11" s="172">
         <v>1</v>
       </c>
-      <c r="T11" s="92">
+      <c r="T11" s="115">
         <v>2</v>
       </c>
-      <c r="U11" s="92">
+      <c r="U11" s="115">
         <v>1</v>
       </c>
-      <c r="V11" s="92" t="s">
+      <c r="V11" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="W11" s="92" t="s">
+      <c r="W11" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="X11" s="92" t="s">
+      <c r="X11" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Y11" s="92" t="s">
+      <c r="Y11" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Z11" s="180" t="s">
+      <c r="Z11" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="AB11" s="178"/>
-      <c r="AC11" s="179"/>
-      <c r="AD11" s="179"/>
-      <c r="AE11" s="179"/>
-      <c r="AF11" s="179"/>
+      <c r="AB11" s="207"/>
+      <c r="AC11" s="208"/>
+      <c r="AD11" s="208"/>
+      <c r="AE11" s="208"/>
+      <c r="AF11" s="208"/>
     </row>
     <row r="12" customHeight="1" spans="1:28">
-      <c r="A12" s="82" t="s">
+      <c r="A12" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="99">
+      <c r="C12" s="122">
         <v>12000</v>
       </c>
-      <c r="D12" s="101">
+      <c r="D12" s="124">
         <v>17500</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="124" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="89"/>
-      <c r="G12" s="87" t="s">
+      <c r="F12" s="112"/>
+      <c r="G12" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="88">
+      <c r="H12" s="111">
         <v>1</v>
       </c>
-      <c r="I12" s="92"/>
-      <c r="J12" s="141">
+      <c r="I12" s="115"/>
+      <c r="J12" s="170">
         <v>4</v>
       </c>
-      <c r="K12" s="142"/>
-      <c r="L12" s="143">
+      <c r="K12" s="171"/>
+      <c r="L12" s="172">
         <v>2</v>
       </c>
-      <c r="M12" s="92">
+      <c r="M12" s="115">
         <v>3</v>
       </c>
-      <c r="N12" s="92">
+      <c r="N12" s="115">
         <v>3</v>
       </c>
-      <c r="O12" s="144">
+      <c r="O12" s="173">
         <v>2</v>
       </c>
-      <c r="P12" s="145">
+      <c r="P12" s="174">
         <v>3</v>
       </c>
-      <c r="Q12" s="147">
+      <c r="Q12" s="176">
         <v>3</v>
       </c>
-      <c r="R12" s="142"/>
-      <c r="S12" s="143">
+      <c r="R12" s="171"/>
+      <c r="S12" s="172">
         <v>2</v>
       </c>
-      <c r="T12" s="92">
+      <c r="T12" s="115">
         <v>2</v>
       </c>
-      <c r="U12" s="92">
+      <c r="U12" s="115">
         <v>2</v>
       </c>
-      <c r="V12" s="87" t="s">
+      <c r="V12" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="W12" s="92" t="s">
+      <c r="W12" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="X12" s="92" t="s">
+      <c r="X12" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Y12" s="92" t="s">
+      <c r="Y12" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Z12" s="180" t="s">
+      <c r="Z12" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="AB12" s="178"/>
+      <c r="AB12" s="207"/>
     </row>
     <row r="13" customHeight="1" spans="1:28">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="83" t="s">
+      <c r="B13" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="99">
+      <c r="C13" s="122">
         <v>13000</v>
       </c>
-      <c r="D13" s="101">
+      <c r="D13" s="124">
         <v>19000</v>
       </c>
-      <c r="E13" s="101">
+      <c r="E13" s="124">
         <v>20500</v>
       </c>
-      <c r="F13" s="89"/>
-      <c r="G13" s="87">
+      <c r="F13" s="112"/>
+      <c r="G13" s="110">
         <v>1</v>
       </c>
-      <c r="H13" s="88">
+      <c r="H13" s="111">
         <v>2</v>
       </c>
-      <c r="I13" s="92"/>
-      <c r="J13" s="146">
+      <c r="I13" s="115"/>
+      <c r="J13" s="175">
         <v>5</v>
       </c>
-      <c r="K13" s="147">
+      <c r="K13" s="176">
         <v>5</v>
       </c>
-      <c r="L13" s="142"/>
-      <c r="M13" s="143">
+      <c r="L13" s="171"/>
+      <c r="M13" s="172">
         <v>3</v>
       </c>
-      <c r="N13" s="92">
+      <c r="N13" s="115">
         <v>4</v>
       </c>
-      <c r="O13" s="92">
+      <c r="O13" s="115">
         <v>4</v>
       </c>
-      <c r="P13" s="144">
+      <c r="P13" s="173">
         <v>3</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="174">
         <v>4</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="176">
         <v>4</v>
       </c>
-      <c r="S13" s="142"/>
-      <c r="T13" s="143">
+      <c r="S13" s="171"/>
+      <c r="T13" s="172">
         <v>2</v>
       </c>
-      <c r="U13" s="92">
+      <c r="U13" s="115">
         <v>3</v>
       </c>
-      <c r="V13" s="92">
+      <c r="V13" s="115">
         <v>3</v>
       </c>
-      <c r="W13" s="92" t="s">
+      <c r="W13" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="X13" s="92" t="s">
+      <c r="X13" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Y13" s="92" t="s">
+      <c r="Y13" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="Z13" s="180" t="s">
+      <c r="Z13" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="AB13" s="178"/>
+      <c r="AB13" s="207"/>
     </row>
     <row r="14" customHeight="1" spans="1:26">
-      <c r="A14" s="90" t="s">
+      <c r="A14" s="113" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="125" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="103">
+      <c r="C14" s="126">
         <v>13000</v>
       </c>
-      <c r="D14" s="104">
+      <c r="D14" s="127">
         <v>19500</v>
       </c>
-      <c r="E14" s="104">
+      <c r="E14" s="127">
         <v>22000</v>
       </c>
-      <c r="F14" s="105"/>
-      <c r="G14" s="106">
+      <c r="F14" s="128"/>
+      <c r="G14" s="129">
         <v>3</v>
       </c>
-      <c r="H14" s="107">
+      <c r="H14" s="130">
         <v>4</v>
       </c>
-      <c r="I14" s="106"/>
-      <c r="J14" s="152">
+      <c r="I14" s="129"/>
+      <c r="J14" s="181">
         <v>9</v>
       </c>
-      <c r="K14" s="153">
+      <c r="K14" s="182">
         <v>9</v>
       </c>
-      <c r="L14" s="154">
+      <c r="L14" s="183">
         <v>11</v>
       </c>
-      <c r="M14" s="155">
+      <c r="M14" s="184">
         <v>11</v>
       </c>
-      <c r="N14" s="156"/>
-      <c r="O14" s="157">
+      <c r="N14" s="185"/>
+      <c r="O14" s="186">
         <v>6</v>
       </c>
-      <c r="P14" s="106">
+      <c r="P14" s="129">
         <v>9</v>
       </c>
-      <c r="Q14" s="106">
+      <c r="Q14" s="129">
         <v>9</v>
       </c>
-      <c r="R14" s="173">
+      <c r="R14" s="202">
         <v>9</v>
       </c>
-      <c r="S14" s="154">
+      <c r="S14" s="183">
         <v>10</v>
       </c>
-      <c r="T14" s="155">
+      <c r="T14" s="184">
         <v>10</v>
       </c>
-      <c r="U14" s="156"/>
-      <c r="V14" s="157">
+      <c r="U14" s="185"/>
+      <c r="V14" s="186">
         <v>5</v>
       </c>
-      <c r="W14" s="106">
+      <c r="W14" s="129">
         <v>8</v>
       </c>
-      <c r="X14" s="106">
+      <c r="X14" s="129">
         <v>8</v>
       </c>
-      <c r="Y14" s="106" t="s">
+      <c r="Y14" s="129" t="s">
         <v>12</v>
       </c>
-      <c r="Z14" s="182" t="s">
+      <c r="Z14" s="211" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:26">
-      <c r="A15" s="46"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="108"/>
-      <c r="L15" s="108"/>
-      <c r="M15" s="108"/>
-      <c r="N15" s="108"/>
-      <c r="O15" s="108"/>
-      <c r="P15" s="108"/>
-      <c r="Q15" s="108"/>
-      <c r="R15" s="108"/>
-      <c r="S15" s="108"/>
-      <c r="T15" s="108"/>
-      <c r="U15" s="108"/>
-      <c r="V15" s="108"/>
-      <c r="W15" s="108"/>
-      <c r="X15" s="108"/>
-      <c r="Y15" s="108"/>
-      <c r="Z15" s="108"/>
+      <c r="A15" s="56"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="131"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="131"/>
+      <c r="M15" s="131"/>
+      <c r="N15" s="131"/>
+      <c r="O15" s="131"/>
+      <c r="P15" s="131"/>
+      <c r="Q15" s="131"/>
+      <c r="R15" s="131"/>
+      <c r="S15" s="131"/>
+      <c r="T15" s="131"/>
+      <c r="U15" s="131"/>
+      <c r="V15" s="131"/>
+      <c r="W15" s="131"/>
+      <c r="X15" s="131"/>
+      <c r="Y15" s="131"/>
+      <c r="Z15" s="131"/>
     </row>
     <row r="16" customHeight="1" spans="1:26">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
-      <c r="H16" s="109"/>
-      <c r="I16" s="109"/>
-      <c r="J16" s="158"/>
-      <c r="K16" s="159" t="s">
+      <c r="B16" s="56"/>
+      <c r="C16" s="131"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="131"/>
+      <c r="G16" s="131"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="187"/>
+      <c r="K16" s="188" t="s">
         <v>32</v>
       </c>
-      <c r="L16" s="159"/>
-      <c r="M16" s="159"/>
-      <c r="N16" s="159"/>
-      <c r="O16" s="160" t="s">
+      <c r="L16" s="188"/>
+      <c r="M16" s="188"/>
+      <c r="N16" s="188"/>
+      <c r="O16" s="189" t="s">
         <v>33</v>
       </c>
-      <c r="P16" s="160"/>
-      <c r="Q16" s="160"/>
-      <c r="R16" s="160"/>
-      <c r="S16" s="160"/>
-      <c r="T16" s="160"/>
-      <c r="U16" s="160"/>
-      <c r="V16" s="160"/>
-      <c r="W16" s="160"/>
-      <c r="X16" s="160"/>
-      <c r="Y16" s="160"/>
-      <c r="Z16" s="160"/>
+      <c r="P16" s="189"/>
+      <c r="Q16" s="189"/>
+      <c r="R16" s="189"/>
+      <c r="S16" s="189"/>
+      <c r="T16" s="189"/>
+      <c r="U16" s="189"/>
+      <c r="V16" s="189"/>
+      <c r="W16" s="189"/>
+      <c r="X16" s="189"/>
+      <c r="Y16" s="189"/>
+      <c r="Z16" s="212"/>
     </row>
     <row r="17" customHeight="1" spans="1:26">
-      <c r="A17" s="46" t="s">
+      <c r="A17" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="108"/>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="108"/>
-      <c r="G17" s="108"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="161"/>
-      <c r="K17" s="159" t="s">
+      <c r="B17" s="56"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="190"/>
+      <c r="K17" s="188" t="s">
         <v>35</v>
       </c>
-      <c r="L17" s="159"/>
-      <c r="M17" s="159"/>
-      <c r="N17" s="159"/>
-      <c r="O17" s="160" t="s">
+      <c r="L17" s="188"/>
+      <c r="M17" s="188"/>
+      <c r="N17" s="188"/>
+      <c r="O17" s="189" t="s">
         <v>36</v>
       </c>
-      <c r="P17" s="160"/>
-      <c r="Q17" s="160"/>
-      <c r="R17" s="160"/>
-      <c r="S17" s="160"/>
-      <c r="T17" s="160"/>
-      <c r="U17" s="160"/>
-      <c r="V17" s="160"/>
-      <c r="W17" s="160"/>
-      <c r="X17" s="160"/>
-      <c r="Y17" s="160"/>
-      <c r="Z17" s="160"/>
+      <c r="P17" s="189"/>
+      <c r="Q17" s="189"/>
+      <c r="R17" s="189"/>
+      <c r="S17" s="189"/>
+      <c r="T17" s="189"/>
+      <c r="U17" s="189"/>
+      <c r="V17" s="189"/>
+      <c r="W17" s="189"/>
+      <c r="X17" s="189"/>
+      <c r="Y17" s="189"/>
+      <c r="Z17" s="212"/>
     </row>
     <row r="18" customHeight="1" spans="1:26">
-      <c r="A18" s="110" t="s">
+      <c r="A18" s="133" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="110"/>
-      <c r="C18" s="110"/>
-      <c r="D18" s="110"/>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="108"/>
-      <c r="H18" s="109"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="162"/>
-      <c r="K18" s="159" t="s">
+      <c r="B18" s="133"/>
+      <c r="C18" s="133"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="132"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="191"/>
+      <c r="K18" s="188" t="s">
         <v>38</v>
       </c>
-      <c r="L18" s="159"/>
-      <c r="M18" s="159"/>
-      <c r="N18" s="159"/>
-      <c r="O18" s="160" t="s">
+      <c r="L18" s="188"/>
+      <c r="M18" s="188"/>
+      <c r="N18" s="188"/>
+      <c r="O18" s="189" t="s">
         <v>39</v>
       </c>
-      <c r="P18" s="160"/>
-      <c r="Q18" s="160"/>
-      <c r="R18" s="160"/>
-      <c r="S18" s="160"/>
-      <c r="T18" s="160"/>
-      <c r="U18" s="160"/>
-      <c r="V18" s="160"/>
-      <c r="W18" s="160"/>
-      <c r="X18" s="160"/>
-      <c r="Y18" s="160"/>
-      <c r="Z18" s="160"/>
+      <c r="P18" s="189"/>
+      <c r="Q18" s="189"/>
+      <c r="R18" s="189"/>
+      <c r="S18" s="189"/>
+      <c r="T18" s="189"/>
+      <c r="U18" s="189"/>
+      <c r="V18" s="189"/>
+      <c r="W18" s="189"/>
+      <c r="X18" s="189"/>
+      <c r="Y18" s="189"/>
+      <c r="Z18" s="212"/>
     </row>
     <row r="19" customHeight="1" spans="1:27">
-      <c r="A19" s="110"/>
-      <c r="B19" s="110"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="163"/>
-      <c r="K19" s="159" t="s">
+      <c r="A19" s="133"/>
+      <c r="B19" s="133"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="132"/>
+      <c r="J19" s="192"/>
+      <c r="K19" s="188" t="s">
         <v>40</v>
       </c>
-      <c r="L19" s="159"/>
-      <c r="M19" s="159"/>
-      <c r="N19" s="159"/>
-      <c r="O19" s="160"/>
-      <c r="P19" s="160"/>
-      <c r="Q19" s="160"/>
-      <c r="R19" s="160"/>
-      <c r="S19" s="160"/>
-      <c r="T19" s="160"/>
-      <c r="U19" s="160"/>
-      <c r="V19" s="160"/>
-      <c r="W19" s="160"/>
-      <c r="X19" s="160"/>
-      <c r="Y19" s="160"/>
-      <c r="Z19" s="160"/>
-      <c r="AA19" s="183"/>
+      <c r="L19" s="188"/>
+      <c r="M19" s="188"/>
+      <c r="N19" s="188"/>
+      <c r="O19" s="189"/>
+      <c r="P19" s="189"/>
+      <c r="Q19" s="189"/>
+      <c r="R19" s="189"/>
+      <c r="S19" s="189"/>
+      <c r="T19" s="189"/>
+      <c r="U19" s="189"/>
+      <c r="V19" s="189"/>
+      <c r="W19" s="189"/>
+      <c r="X19" s="189"/>
+      <c r="Y19" s="189"/>
+      <c r="Z19" s="212"/>
+      <c r="AA19" s="213"/>
     </row>
     <row r="20" customHeight="1" spans="1:27">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="133" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="110"/>
-      <c r="C20" s="110"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="108"/>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="164"/>
-      <c r="K20" s="33" t="s">
+      <c r="B20" s="133"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="132"/>
+      <c r="I20" s="132"/>
+      <c r="J20" s="193"/>
+      <c r="K20" s="189" t="s">
         <v>42</v>
       </c>
-      <c r="L20" s="165"/>
-      <c r="M20" s="165"/>
-      <c r="N20" s="165"/>
-      <c r="O20" s="33" t="s">
+      <c r="L20" s="194"/>
+      <c r="M20" s="194"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="189" t="s">
         <v>43</v>
       </c>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="33"/>
-      <c r="V20" s="33"/>
-      <c r="W20" s="33"/>
-      <c r="X20" s="33"/>
-      <c r="Y20" s="33"/>
-      <c r="Z20" s="33"/>
-      <c r="AA20" s="183"/>
+      <c r="P20" s="189"/>
+      <c r="Q20" s="189"/>
+      <c r="R20" s="189"/>
+      <c r="S20" s="189"/>
+      <c r="T20" s="189"/>
+      <c r="U20" s="189"/>
+      <c r="V20" s="189"/>
+      <c r="W20" s="189"/>
+      <c r="X20" s="189"/>
+      <c r="Y20" s="189"/>
+      <c r="Z20" s="212"/>
+      <c r="AA20" s="213"/>
     </row>
     <row r="21" customHeight="1" spans="1:27">
-      <c r="A21" s="111"/>
-      <c r="B21" s="111"/>
-      <c r="G21" s="112"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="166"/>
-      <c r="J21" s="167"/>
-      <c r="K21" s="168" t="s">
+      <c r="A21" s="134"/>
+      <c r="B21" s="134"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="136"/>
+      <c r="I21" s="195"/>
+      <c r="J21" s="196"/>
+      <c r="K21" s="197" t="s">
         <v>44</v>
       </c>
-      <c r="L21" s="169"/>
-      <c r="M21" s="169"/>
-      <c r="N21" s="169"/>
-      <c r="O21" s="168" t="s">
+      <c r="L21" s="198"/>
+      <c r="M21" s="198"/>
+      <c r="N21" s="198"/>
+      <c r="O21" s="197" t="s">
         <v>45</v>
       </c>
-      <c r="P21" s="168"/>
-      <c r="Q21" s="168"/>
-      <c r="R21" s="168"/>
-      <c r="S21" s="168"/>
-      <c r="T21" s="168"/>
-      <c r="U21" s="168"/>
-      <c r="V21" s="168"/>
-      <c r="W21" s="168"/>
-      <c r="X21" s="168"/>
-      <c r="Y21" s="168"/>
-      <c r="Z21" s="168"/>
-      <c r="AA21" s="183"/>
+      <c r="P21" s="197"/>
+      <c r="Q21" s="197"/>
+      <c r="R21" s="197"/>
+      <c r="S21" s="197"/>
+      <c r="T21" s="197"/>
+      <c r="U21" s="197"/>
+      <c r="V21" s="197"/>
+      <c r="W21" s="197"/>
+      <c r="X21" s="197"/>
+      <c r="Y21" s="197"/>
+      <c r="Z21" s="214"/>
+      <c r="AA21" s="213"/>
     </row>
     <row r="22" customHeight="1" spans="1:27">
-      <c r="A22" s="111"/>
-      <c r="B22" s="111"/>
-      <c r="G22" s="112"/>
-      <c r="H22" s="113"/>
-      <c r="I22" s="166"/>
-      <c r="J22" s="170"/>
-      <c r="K22" s="170"/>
-      <c r="L22" s="170"/>
-      <c r="M22" s="171"/>
-      <c r="N22" s="171"/>
-      <c r="O22" s="171"/>
-      <c r="P22" s="170"/>
-      <c r="Q22" s="170"/>
-      <c r="R22" s="170"/>
-      <c r="S22" s="170"/>
-      <c r="T22" s="171"/>
-      <c r="U22" s="171"/>
-      <c r="V22" s="171"/>
-      <c r="W22" s="171"/>
-      <c r="X22" s="171"/>
-      <c r="Y22" s="171"/>
-      <c r="Z22" s="171"/>
-      <c r="AA22" s="183"/>
+      <c r="A22" s="134"/>
+      <c r="B22" s="134"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="195"/>
+      <c r="J22" s="199"/>
+      <c r="K22" s="199"/>
+      <c r="L22" s="199"/>
+      <c r="M22" s="200"/>
+      <c r="N22" s="200"/>
+      <c r="O22" s="200"/>
+      <c r="P22" s="199"/>
+      <c r="Q22" s="199"/>
+      <c r="R22" s="199"/>
+      <c r="S22" s="199"/>
+      <c r="T22" s="200"/>
+      <c r="U22" s="200"/>
+      <c r="V22" s="200"/>
+      <c r="W22" s="200"/>
+      <c r="X22" s="200"/>
+      <c r="Y22" s="200"/>
+      <c r="Z22" s="200"/>
+      <c r="AA22" s="213"/>
     </row>
     <row r="23" customHeight="1" spans="2:26">
-      <c r="B23" s="114" t="s">
+      <c r="B23" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="115" t="s">
+      <c r="C23" s="138" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115" t="s">
+      <c r="D23" s="138"/>
+      <c r="E23" s="138"/>
+      <c r="F23" s="138"/>
+      <c r="G23" s="138" t="s">
         <v>48</v>
       </c>
-      <c r="H23" s="115"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="115"/>
-      <c r="K23" s="115"/>
-      <c r="L23" s="115"/>
-      <c r="M23" s="115"/>
-      <c r="N23" s="115"/>
-      <c r="O23" s="115"/>
-      <c r="P23" s="115"/>
-      <c r="Q23" s="115"/>
-      <c r="R23" s="115"/>
-      <c r="S23" s="115"/>
-      <c r="T23" s="115"/>
-      <c r="U23" s="115"/>
-      <c r="V23" s="115"/>
-      <c r="W23" s="115"/>
-      <c r="X23" s="115"/>
-      <c r="Y23" s="115"/>
-      <c r="Z23" s="115"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="138"/>
+      <c r="K23" s="138"/>
+      <c r="L23" s="138"/>
+      <c r="M23" s="138"/>
+      <c r="N23" s="138"/>
+      <c r="O23" s="138"/>
+      <c r="P23" s="138"/>
+      <c r="Q23" s="138"/>
+      <c r="R23" s="138"/>
+      <c r="S23" s="138"/>
+      <c r="T23" s="138"/>
+      <c r="U23" s="138"/>
+      <c r="V23" s="138"/>
+      <c r="W23" s="138"/>
+      <c r="X23" s="138"/>
+      <c r="Y23" s="138"/>
+      <c r="Z23" s="215"/>
     </row>
     <row r="24" customHeight="1" spans="2:26">
-      <c r="B24" s="116" t="s">
+      <c r="B24" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="117" t="s">
+      <c r="C24" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="117" t="s">
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140" t="s">
         <v>51</v>
       </c>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="111"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
-      <c r="W24" s="111"/>
-      <c r="X24" s="111"/>
-      <c r="Y24" s="111"/>
-      <c r="Z24" s="111"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="134"/>
+      <c r="J24" s="134"/>
+      <c r="K24" s="134"/>
+      <c r="L24" s="134"/>
+      <c r="M24" s="134"/>
+      <c r="N24" s="134"/>
+      <c r="O24" s="134"/>
+      <c r="P24" s="134"/>
+      <c r="Q24" s="134"/>
+      <c r="R24" s="134"/>
+      <c r="S24" s="134"/>
+      <c r="T24" s="134"/>
+      <c r="U24" s="134"/>
+      <c r="V24" s="134"/>
+      <c r="W24" s="134"/>
+      <c r="X24" s="134"/>
+      <c r="Y24" s="134"/>
+      <c r="Z24" s="216"/>
     </row>
     <row r="25" customHeight="1" spans="2:26">
-      <c r="B25" s="116" t="s">
+      <c r="B25" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="117" t="s">
+      <c r="C25" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="117"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117" t="s">
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="111"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="111"/>
-      <c r="R25" s="111"/>
-      <c r="S25" s="111"/>
-      <c r="T25" s="111"/>
-      <c r="U25" s="111"/>
-      <c r="V25" s="111"/>
-      <c r="W25" s="111"/>
-      <c r="X25" s="111"/>
-      <c r="Y25" s="111"/>
-      <c r="Z25" s="111"/>
+      <c r="H25" s="134"/>
+      <c r="I25" s="134"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="134"/>
+      <c r="L25" s="134"/>
+      <c r="M25" s="134"/>
+      <c r="N25" s="134"/>
+      <c r="O25" s="134"/>
+      <c r="P25" s="134"/>
+      <c r="Q25" s="134"/>
+      <c r="R25" s="134"/>
+      <c r="S25" s="134"/>
+      <c r="T25" s="134"/>
+      <c r="U25" s="134"/>
+      <c r="V25" s="134"/>
+      <c r="W25" s="134"/>
+      <c r="X25" s="134"/>
+      <c r="Y25" s="134"/>
+      <c r="Z25" s="216"/>
     </row>
     <row r="26" customHeight="1" spans="2:26">
-      <c r="B26" s="116" t="s">
+      <c r="B26" s="139" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="117" t="s">
+      <c r="C26" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117" t="s">
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140" t="s">
         <v>55</v>
       </c>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="111"/>
-      <c r="L26" s="111"/>
-      <c r="M26" s="111"/>
-      <c r="N26" s="111"/>
-      <c r="O26" s="111"/>
-      <c r="P26" s="111"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="111"/>
-      <c r="S26" s="111"/>
-      <c r="T26" s="111"/>
-      <c r="U26" s="111"/>
-      <c r="V26" s="111"/>
-      <c r="W26" s="111"/>
-      <c r="X26" s="111"/>
-      <c r="Y26" s="111"/>
-      <c r="Z26" s="111"/>
+      <c r="H26" s="134"/>
+      <c r="I26" s="134"/>
+      <c r="J26" s="134"/>
+      <c r="K26" s="134"/>
+      <c r="L26" s="134"/>
+      <c r="M26" s="134"/>
+      <c r="N26" s="134"/>
+      <c r="O26" s="134"/>
+      <c r="P26" s="134"/>
+      <c r="Q26" s="134"/>
+      <c r="R26" s="134"/>
+      <c r="S26" s="134"/>
+      <c r="T26" s="134"/>
+      <c r="U26" s="134"/>
+      <c r="V26" s="134"/>
+      <c r="W26" s="134"/>
+      <c r="X26" s="134"/>
+      <c r="Y26" s="134"/>
+      <c r="Z26" s="216"/>
     </row>
     <row r="27" customHeight="1" spans="2:26">
-      <c r="B27" s="116" t="s">
+      <c r="B27" s="139" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="117" t="s">
+      <c r="C27" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="117"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="117"/>
-      <c r="G27" s="117" t="s">
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
+      <c r="G27" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="111"/>
-      <c r="N27" s="111"/>
-      <c r="O27" s="111"/>
-      <c r="P27" s="111"/>
-      <c r="Q27" s="111"/>
-      <c r="R27" s="111"/>
-      <c r="S27" s="111"/>
-      <c r="T27" s="111"/>
-      <c r="U27" s="111"/>
-      <c r="V27" s="111"/>
-      <c r="W27" s="111"/>
-      <c r="X27" s="111"/>
-      <c r="Y27" s="111"/>
-      <c r="Z27" s="111"/>
+      <c r="H27" s="134"/>
+      <c r="I27" s="134"/>
+      <c r="J27" s="134"/>
+      <c r="K27" s="134"/>
+      <c r="L27" s="134"/>
+      <c r="M27" s="134"/>
+      <c r="N27" s="134"/>
+      <c r="O27" s="134"/>
+      <c r="P27" s="134"/>
+      <c r="Q27" s="134"/>
+      <c r="R27" s="134"/>
+      <c r="S27" s="134"/>
+      <c r="T27" s="134"/>
+      <c r="U27" s="134"/>
+      <c r="V27" s="134"/>
+      <c r="W27" s="134"/>
+      <c r="X27" s="134"/>
+      <c r="Y27" s="134"/>
+      <c r="Z27" s="216"/>
     </row>
     <row r="28" customHeight="1" spans="2:26">
-      <c r="B28" s="116" t="s">
+      <c r="B28" s="139" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="117" t="s">
+      <c r="C28" s="140" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="117"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="117"/>
-      <c r="G28" s="117" t="s">
+      <c r="D28" s="140"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="140" t="s">
         <v>61</v>
       </c>
-      <c r="H28" s="111"/>
-      <c r="I28" s="111"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="111"/>
-      <c r="L28" s="111"/>
-      <c r="M28" s="111"/>
-      <c r="N28" s="111"/>
-      <c r="O28" s="111"/>
-      <c r="P28" s="111"/>
-      <c r="Q28" s="111"/>
-      <c r="R28" s="111"/>
-      <c r="S28" s="111"/>
-      <c r="T28" s="111"/>
-      <c r="U28" s="111"/>
-      <c r="V28" s="111"/>
-      <c r="W28" s="111"/>
-      <c r="X28" s="111"/>
-      <c r="Y28" s="111"/>
-      <c r="Z28" s="111"/>
+      <c r="H28" s="134"/>
+      <c r="I28" s="134"/>
+      <c r="J28" s="134"/>
+      <c r="K28" s="134"/>
+      <c r="L28" s="134"/>
+      <c r="M28" s="134"/>
+      <c r="N28" s="134"/>
+      <c r="O28" s="134"/>
+      <c r="P28" s="134"/>
+      <c r="Q28" s="134"/>
+      <c r="R28" s="134"/>
+      <c r="S28" s="134"/>
+      <c r="T28" s="134"/>
+      <c r="U28" s="134"/>
+      <c r="V28" s="134"/>
+      <c r="W28" s="134"/>
+      <c r="X28" s="134"/>
+      <c r="Y28" s="134"/>
+      <c r="Z28" s="216"/>
     </row>
     <row r="29" customHeight="1" spans="2:26">
-      <c r="B29" s="116" t="s">
+      <c r="B29" s="139" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="117" t="s">
+      <c r="C29" s="140" t="s">
         <v>63</v>
       </c>
-      <c r="D29" s="117"/>
-      <c r="E29" s="117"/>
-      <c r="F29" s="117"/>
-      <c r="G29" s="117" t="s">
+      <c r="D29" s="140"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="H29" s="111"/>
-      <c r="I29" s="111"/>
-      <c r="J29" s="111"/>
-      <c r="K29" s="111"/>
-      <c r="L29" s="111"/>
-      <c r="M29" s="111"/>
-      <c r="N29" s="111"/>
-      <c r="O29" s="111"/>
-      <c r="P29" s="111"/>
-      <c r="Q29" s="111"/>
-      <c r="R29" s="111"/>
-      <c r="S29" s="111"/>
-      <c r="T29" s="111"/>
-      <c r="U29" s="111"/>
-      <c r="V29" s="111"/>
-      <c r="W29" s="111"/>
-      <c r="X29" s="111"/>
-      <c r="Y29" s="111"/>
-      <c r="Z29" s="111"/>
+      <c r="H29" s="134"/>
+      <c r="I29" s="134"/>
+      <c r="J29" s="134"/>
+      <c r="K29" s="134"/>
+      <c r="L29" s="134"/>
+      <c r="M29" s="134"/>
+      <c r="N29" s="134"/>
+      <c r="O29" s="134"/>
+      <c r="P29" s="134"/>
+      <c r="Q29" s="134"/>
+      <c r="R29" s="134"/>
+      <c r="S29" s="134"/>
+      <c r="T29" s="134"/>
+      <c r="U29" s="134"/>
+      <c r="V29" s="134"/>
+      <c r="W29" s="134"/>
+      <c r="X29" s="134"/>
+      <c r="Y29" s="134"/>
+      <c r="Z29" s="216"/>
     </row>
     <row r="30" customHeight="1" spans="2:26">
-      <c r="B30" s="116" t="s">
+      <c r="B30" s="139" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="117" t="s">
+      <c r="C30" s="140" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="117"/>
-      <c r="E30" s="117"/>
-      <c r="F30" s="117"/>
-      <c r="G30" s="117" t="s">
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="140"/>
+      <c r="G30" s="140" t="s">
         <v>67</v>
       </c>
-      <c r="H30" s="111"/>
-      <c r="I30" s="111"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="111"/>
-      <c r="L30" s="111"/>
-      <c r="M30" s="111"/>
-      <c r="N30" s="111"/>
-      <c r="O30" s="111"/>
-      <c r="P30" s="111"/>
-      <c r="Q30" s="111"/>
-      <c r="R30" s="111"/>
-      <c r="S30" s="111"/>
-      <c r="T30" s="111"/>
-      <c r="U30" s="111"/>
-      <c r="V30" s="111"/>
-      <c r="W30" s="111"/>
-      <c r="X30" s="111"/>
-      <c r="Y30" s="111"/>
-      <c r="Z30" s="111"/>
+      <c r="H30" s="134"/>
+      <c r="I30" s="134"/>
+      <c r="J30" s="134"/>
+      <c r="K30" s="134"/>
+      <c r="L30" s="134"/>
+      <c r="M30" s="134"/>
+      <c r="N30" s="134"/>
+      <c r="O30" s="134"/>
+      <c r="P30" s="134"/>
+      <c r="Q30" s="134"/>
+      <c r="R30" s="134"/>
+      <c r="S30" s="134"/>
+      <c r="T30" s="134"/>
+      <c r="U30" s="134"/>
+      <c r="V30" s="134"/>
+      <c r="W30" s="134"/>
+      <c r="X30" s="134"/>
+      <c r="Y30" s="134"/>
+      <c r="Z30" s="216"/>
     </row>
     <row r="31" customHeight="1" spans="2:26">
-      <c r="B31" s="116" t="s">
+      <c r="B31" s="141" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="117" t="s">
+      <c r="C31" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="117"/>
-      <c r="E31" s="117"/>
-      <c r="F31" s="117"/>
-      <c r="G31" s="117" t="s">
+      <c r="D31" s="142"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="142" t="s">
         <v>70</v>
       </c>
-      <c r="H31" s="111"/>
-      <c r="I31" s="111"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="111"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="111"/>
-      <c r="N31" s="111"/>
-      <c r="O31" s="111"/>
-      <c r="P31" s="111"/>
-      <c r="Q31" s="111"/>
-      <c r="R31" s="111"/>
-      <c r="S31" s="111"/>
-      <c r="T31" s="111"/>
-      <c r="U31" s="111"/>
-      <c r="V31" s="111"/>
-      <c r="W31" s="111"/>
-      <c r="X31" s="111"/>
-      <c r="Y31" s="111"/>
-      <c r="Z31" s="111"/>
+      <c r="H31" s="143"/>
+      <c r="I31" s="143"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="143"/>
+      <c r="L31" s="143"/>
+      <c r="M31" s="143"/>
+      <c r="N31" s="143"/>
+      <c r="O31" s="143"/>
+      <c r="P31" s="143"/>
+      <c r="Q31" s="143"/>
+      <c r="R31" s="143"/>
+      <c r="S31" s="143"/>
+      <c r="T31" s="143"/>
+      <c r="U31" s="143"/>
+      <c r="V31" s="143"/>
+      <c r="W31" s="143"/>
+      <c r="X31" s="143"/>
+      <c r="Y31" s="143"/>
+      <c r="Z31" s="217"/>
     </row>
     <row r="33" customHeight="1" spans="2:26">
-      <c r="B33" s="118" t="s">
+      <c r="B33" s="144" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="119" t="s">
+      <c r="C33" s="145" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="119"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="119" t="s">
+      <c r="D33" s="145"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="145"/>
+      <c r="G33" s="145" t="s">
         <v>48</v>
       </c>
-      <c r="H33" s="119"/>
-      <c r="I33" s="119"/>
-      <c r="J33" s="119"/>
-      <c r="K33" s="119"/>
-      <c r="L33" s="119"/>
-      <c r="M33" s="119"/>
-      <c r="N33" s="119"/>
-      <c r="O33" s="119"/>
-      <c r="P33" s="119"/>
-      <c r="Q33" s="119"/>
-      <c r="R33" s="119"/>
-      <c r="S33" s="119"/>
-      <c r="T33" s="119"/>
-      <c r="U33" s="119"/>
-      <c r="V33" s="119"/>
-      <c r="W33" s="119"/>
-      <c r="X33" s="119"/>
-      <c r="Y33" s="119"/>
-      <c r="Z33" s="119"/>
+      <c r="H33" s="145"/>
+      <c r="I33" s="145"/>
+      <c r="J33" s="145"/>
+      <c r="K33" s="145"/>
+      <c r="L33" s="145"/>
+      <c r="M33" s="145"/>
+      <c r="N33" s="145"/>
+      <c r="O33" s="145"/>
+      <c r="P33" s="145"/>
+      <c r="Q33" s="145"/>
+      <c r="R33" s="145"/>
+      <c r="S33" s="145"/>
+      <c r="T33" s="145"/>
+      <c r="U33" s="145"/>
+      <c r="V33" s="145"/>
+      <c r="W33" s="145"/>
+      <c r="X33" s="145"/>
+      <c r="Y33" s="145"/>
+      <c r="Z33" s="218"/>
     </row>
     <row r="34" customHeight="1" spans="2:26">
-      <c r="B34" s="120" t="s">
+      <c r="B34" s="146" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="117" t="s">
+      <c r="C34" s="140" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="117"/>
-      <c r="E34" s="117"/>
-      <c r="F34" s="117"/>
-      <c r="G34" s="117" t="s">
+      <c r="D34" s="140"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="140" t="s">
         <v>73</v>
       </c>
-      <c r="H34" s="111"/>
-      <c r="I34" s="111"/>
-      <c r="J34" s="111"/>
-      <c r="K34" s="111"/>
-      <c r="L34" s="111"/>
-      <c r="M34" s="111"/>
-      <c r="N34" s="111"/>
-      <c r="O34" s="111"/>
-      <c r="P34" s="111"/>
-      <c r="Q34" s="111"/>
-      <c r="R34" s="111"/>
-      <c r="S34" s="111"/>
-      <c r="T34" s="111"/>
-      <c r="U34" s="111"/>
-      <c r="V34" s="111"/>
-      <c r="W34" s="111"/>
-      <c r="X34" s="111"/>
-      <c r="Y34" s="111"/>
-      <c r="Z34" s="111"/>
+      <c r="H34" s="134"/>
+      <c r="I34" s="134"/>
+      <c r="J34" s="134"/>
+      <c r="K34" s="134"/>
+      <c r="L34" s="134"/>
+      <c r="M34" s="134"/>
+      <c r="N34" s="134"/>
+      <c r="O34" s="134"/>
+      <c r="P34" s="134"/>
+      <c r="Q34" s="134"/>
+      <c r="R34" s="134"/>
+      <c r="S34" s="134"/>
+      <c r="T34" s="134"/>
+      <c r="U34" s="134"/>
+      <c r="V34" s="134"/>
+      <c r="W34" s="134"/>
+      <c r="X34" s="134"/>
+      <c r="Y34" s="134"/>
+      <c r="Z34" s="216"/>
     </row>
     <row r="35" customHeight="1" spans="2:26">
-      <c r="B35" s="120" t="s">
+      <c r="B35" s="146" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="117" t="s">
+      <c r="C35" s="140" t="s">
         <v>74</v>
       </c>
-      <c r="D35" s="117"/>
-      <c r="E35" s="117"/>
-      <c r="F35" s="117"/>
-      <c r="G35" s="117" t="s">
+      <c r="D35" s="140"/>
+      <c r="E35" s="140"/>
+      <c r="F35" s="140"/>
+      <c r="G35" s="140" t="s">
         <v>75</v>
       </c>
-      <c r="H35" s="111"/>
-      <c r="I35" s="111"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="111"/>
-      <c r="M35" s="111"/>
-      <c r="N35" s="111"/>
-      <c r="O35" s="111"/>
-      <c r="P35" s="111"/>
-      <c r="Q35" s="111"/>
-      <c r="R35" s="111"/>
-      <c r="S35" s="111"/>
-      <c r="T35" s="111"/>
-      <c r="U35" s="111"/>
-      <c r="V35" s="111"/>
-      <c r="W35" s="111"/>
-      <c r="X35" s="111"/>
-      <c r="Y35" s="111"/>
-      <c r="Z35" s="111"/>
+      <c r="H35" s="134"/>
+      <c r="I35" s="134"/>
+      <c r="J35" s="134"/>
+      <c r="K35" s="134"/>
+      <c r="L35" s="134"/>
+      <c r="M35" s="134"/>
+      <c r="N35" s="134"/>
+      <c r="O35" s="134"/>
+      <c r="P35" s="134"/>
+      <c r="Q35" s="134"/>
+      <c r="R35" s="134"/>
+      <c r="S35" s="134"/>
+      <c r="T35" s="134"/>
+      <c r="U35" s="134"/>
+      <c r="V35" s="134"/>
+      <c r="W35" s="134"/>
+      <c r="X35" s="134"/>
+      <c r="Y35" s="134"/>
+      <c r="Z35" s="216"/>
     </row>
     <row r="36" customHeight="1" spans="2:26">
-      <c r="B36" s="120" t="s">
+      <c r="B36" s="146" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="117" t="s">
+      <c r="C36" s="140" t="s">
         <v>76</v>
       </c>
-      <c r="D36" s="117"/>
-      <c r="E36" s="117"/>
-      <c r="F36" s="117"/>
-      <c r="G36" s="117" t="s">
+      <c r="D36" s="140"/>
+      <c r="E36" s="140"/>
+      <c r="F36" s="140"/>
+      <c r="G36" s="140" t="s">
         <v>77</v>
       </c>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="111"/>
-      <c r="N36" s="111"/>
-      <c r="O36" s="111"/>
-      <c r="P36" s="111"/>
-      <c r="Q36" s="111"/>
-      <c r="R36" s="111"/>
-      <c r="S36" s="111"/>
-      <c r="T36" s="111"/>
-      <c r="U36" s="111"/>
-      <c r="V36" s="111"/>
-      <c r="W36" s="111"/>
-      <c r="X36" s="111"/>
-      <c r="Y36" s="111"/>
-      <c r="Z36" s="111"/>
+      <c r="H36" s="134"/>
+      <c r="I36" s="134"/>
+      <c r="J36" s="134"/>
+      <c r="K36" s="134"/>
+      <c r="L36" s="134"/>
+      <c r="M36" s="134"/>
+      <c r="N36" s="134"/>
+      <c r="O36" s="134"/>
+      <c r="P36" s="134"/>
+      <c r="Q36" s="134"/>
+      <c r="R36" s="134"/>
+      <c r="S36" s="134"/>
+      <c r="T36" s="134"/>
+      <c r="U36" s="134"/>
+      <c r="V36" s="134"/>
+      <c r="W36" s="134"/>
+      <c r="X36" s="134"/>
+      <c r="Y36" s="134"/>
+      <c r="Z36" s="216"/>
     </row>
     <row r="37" customHeight="1" spans="2:26">
-      <c r="B37" s="120" t="s">
+      <c r="B37" s="146" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="117" t="s">
+      <c r="C37" s="140" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="117"/>
-      <c r="E37" s="117"/>
-      <c r="F37" s="117"/>
-      <c r="G37" s="117" t="s">
+      <c r="D37" s="140"/>
+      <c r="E37" s="140"/>
+      <c r="F37" s="140"/>
+      <c r="G37" s="140" t="s">
         <v>80</v>
       </c>
-      <c r="H37" s="111"/>
-      <c r="I37" s="111"/>
-      <c r="J37" s="111"/>
-      <c r="K37" s="111"/>
-      <c r="L37" s="111"/>
-      <c r="M37" s="111"/>
-      <c r="N37" s="111"/>
-      <c r="O37" s="111"/>
-      <c r="P37" s="111"/>
-      <c r="Q37" s="111"/>
-      <c r="R37" s="111"/>
-      <c r="S37" s="111"/>
-      <c r="T37" s="111"/>
-      <c r="U37" s="111"/>
-      <c r="V37" s="111"/>
-      <c r="W37" s="111"/>
-      <c r="X37" s="111"/>
-      <c r="Y37" s="111"/>
-      <c r="Z37" s="111"/>
+      <c r="H37" s="134"/>
+      <c r="I37" s="134"/>
+      <c r="J37" s="134"/>
+      <c r="K37" s="134"/>
+      <c r="L37" s="134"/>
+      <c r="M37" s="134"/>
+      <c r="N37" s="134"/>
+      <c r="O37" s="134"/>
+      <c r="P37" s="134"/>
+      <c r="Q37" s="134"/>
+      <c r="R37" s="134"/>
+      <c r="S37" s="134"/>
+      <c r="T37" s="134"/>
+      <c r="U37" s="134"/>
+      <c r="V37" s="134"/>
+      <c r="W37" s="134"/>
+      <c r="X37" s="134"/>
+      <c r="Y37" s="134"/>
+      <c r="Z37" s="216"/>
     </row>
     <row r="38" customHeight="1" spans="2:26">
-      <c r="B38" s="120" t="s">
+      <c r="B38" s="147" t="s">
         <v>81</v>
       </c>
-      <c r="C38" s="117" t="s">
+      <c r="C38" s="142" t="s">
         <v>82</v>
       </c>
-      <c r="D38" s="117"/>
-      <c r="E38" s="117"/>
-      <c r="F38" s="117"/>
-      <c r="G38" s="117" t="s">
+      <c r="D38" s="142"/>
+      <c r="E38" s="142"/>
+      <c r="F38" s="142"/>
+      <c r="G38" s="142" t="s">
         <v>83</v>
       </c>
-      <c r="H38" s="111"/>
-      <c r="I38" s="111"/>
-      <c r="J38" s="111"/>
-      <c r="K38" s="111"/>
-      <c r="L38" s="111"/>
-      <c r="M38" s="111"/>
-      <c r="N38" s="111"/>
-      <c r="O38" s="111"/>
-      <c r="P38" s="111"/>
-      <c r="Q38" s="111"/>
-      <c r="R38" s="111"/>
-      <c r="S38" s="111"/>
-      <c r="T38" s="111"/>
-      <c r="U38" s="111"/>
-      <c r="V38" s="111"/>
-      <c r="W38" s="111"/>
-      <c r="X38" s="111"/>
-      <c r="Y38" s="111"/>
-      <c r="Z38" s="111"/>
+      <c r="H38" s="143"/>
+      <c r="I38" s="143"/>
+      <c r="J38" s="143"/>
+      <c r="K38" s="143"/>
+      <c r="L38" s="143"/>
+      <c r="M38" s="143"/>
+      <c r="N38" s="143"/>
+      <c r="O38" s="143"/>
+      <c r="P38" s="143"/>
+      <c r="Q38" s="143"/>
+      <c r="R38" s="143"/>
+      <c r="S38" s="143"/>
+      <c r="T38" s="143"/>
+      <c r="U38" s="143"/>
+      <c r="V38" s="143"/>
+      <c r="W38" s="143"/>
+      <c r="X38" s="143"/>
+      <c r="Y38" s="143"/>
+      <c r="Z38" s="217"/>
     </row>
     <row r="40" customHeight="1" spans="2:26">
-      <c r="B40" s="121" t="s">
+      <c r="B40" s="148" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="122" t="s">
+      <c r="C40" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="D40" s="122"/>
-      <c r="E40" s="122"/>
-      <c r="F40" s="122"/>
-      <c r="G40" s="122" t="s">
+      <c r="D40" s="149"/>
+      <c r="E40" s="149"/>
+      <c r="F40" s="149"/>
+      <c r="G40" s="149" t="s">
         <v>48</v>
       </c>
-      <c r="H40" s="122"/>
-      <c r="I40" s="122"/>
-      <c r="J40" s="122"/>
-      <c r="K40" s="122"/>
-      <c r="L40" s="122"/>
-      <c r="M40" s="122"/>
-      <c r="N40" s="122"/>
-      <c r="O40" s="122"/>
-      <c r="P40" s="122"/>
-      <c r="Q40" s="122"/>
-      <c r="R40" s="122"/>
-      <c r="S40" s="122"/>
-      <c r="T40" s="122"/>
-      <c r="U40" s="122"/>
-      <c r="V40" s="122"/>
-      <c r="W40" s="122"/>
-      <c r="X40" s="122"/>
-      <c r="Y40" s="122"/>
-      <c r="Z40" s="122"/>
+      <c r="H40" s="149"/>
+      <c r="I40" s="149"/>
+      <c r="J40" s="149"/>
+      <c r="K40" s="149"/>
+      <c r="L40" s="149"/>
+      <c r="M40" s="149"/>
+      <c r="N40" s="149"/>
+      <c r="O40" s="149"/>
+      <c r="P40" s="149"/>
+      <c r="Q40" s="149"/>
+      <c r="R40" s="149"/>
+      <c r="S40" s="149"/>
+      <c r="T40" s="149"/>
+      <c r="U40" s="149"/>
+      <c r="V40" s="149"/>
+      <c r="W40" s="149"/>
+      <c r="X40" s="149"/>
+      <c r="Y40" s="149"/>
+      <c r="Z40" s="219"/>
     </row>
     <row r="41" customHeight="1" spans="2:26">
-      <c r="B41" s="123" t="s">
+      <c r="B41" s="150" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="117" t="s">
+      <c r="C41" s="140" t="s">
         <v>85</v>
       </c>
-      <c r="D41" s="117"/>
-      <c r="E41" s="117"/>
-      <c r="F41" s="117"/>
-      <c r="G41" s="117" t="s">
+      <c r="D41" s="140"/>
+      <c r="E41" s="140"/>
+      <c r="F41" s="140"/>
+      <c r="G41" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="H41" s="111"/>
-      <c r="I41" s="111"/>
-      <c r="J41" s="111"/>
-      <c r="K41" s="111"/>
-      <c r="L41" s="111"/>
-      <c r="M41" s="111"/>
-      <c r="N41" s="111"/>
-      <c r="O41" s="111"/>
-      <c r="P41" s="111"/>
-      <c r="Q41" s="111"/>
-      <c r="R41" s="111"/>
-      <c r="S41" s="111"/>
-      <c r="T41" s="111"/>
-      <c r="U41" s="111"/>
-      <c r="V41" s="111"/>
-      <c r="W41" s="111"/>
-      <c r="X41" s="111"/>
-      <c r="Y41" s="111"/>
-      <c r="Z41" s="111"/>
+      <c r="H41" s="134"/>
+      <c r="I41" s="134"/>
+      <c r="J41" s="134"/>
+      <c r="K41" s="134"/>
+      <c r="L41" s="134"/>
+      <c r="M41" s="134"/>
+      <c r="N41" s="134"/>
+      <c r="O41" s="134"/>
+      <c r="P41" s="134"/>
+      <c r="Q41" s="134"/>
+      <c r="R41" s="134"/>
+      <c r="S41" s="134"/>
+      <c r="T41" s="134"/>
+      <c r="U41" s="134"/>
+      <c r="V41" s="134"/>
+      <c r="W41" s="134"/>
+      <c r="X41" s="134"/>
+      <c r="Y41" s="134"/>
+      <c r="Z41" s="216"/>
     </row>
     <row r="42" customHeight="1" spans="2:26">
-      <c r="B42" s="123" t="s">
+      <c r="B42" s="150" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="117" t="s">
+      <c r="C42" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="D42" s="117"/>
-      <c r="E42" s="117"/>
-      <c r="F42" s="117"/>
-      <c r="G42" s="117" t="s">
+      <c r="D42" s="140"/>
+      <c r="E42" s="140"/>
+      <c r="F42" s="140"/>
+      <c r="G42" s="140" t="s">
         <v>89</v>
       </c>
-      <c r="H42" s="111"/>
-      <c r="I42" s="111"/>
-      <c r="J42" s="111"/>
-      <c r="K42" s="111"/>
-      <c r="L42" s="111"/>
-      <c r="M42" s="111"/>
-      <c r="N42" s="111"/>
-      <c r="O42" s="111"/>
-      <c r="P42" s="111"/>
-      <c r="Q42" s="111"/>
-      <c r="R42" s="111"/>
-      <c r="S42" s="111"/>
-      <c r="T42" s="111"/>
-      <c r="U42" s="111"/>
-      <c r="V42" s="111"/>
-      <c r="W42" s="111"/>
-      <c r="X42" s="111"/>
-      <c r="Y42" s="111"/>
-      <c r="Z42" s="111"/>
+      <c r="H42" s="134"/>
+      <c r="I42" s="134"/>
+      <c r="J42" s="134"/>
+      <c r="K42" s="134"/>
+      <c r="L42" s="134"/>
+      <c r="M42" s="134"/>
+      <c r="N42" s="134"/>
+      <c r="O42" s="134"/>
+      <c r="P42" s="134"/>
+      <c r="Q42" s="134"/>
+      <c r="R42" s="134"/>
+      <c r="S42" s="134"/>
+      <c r="T42" s="134"/>
+      <c r="U42" s="134"/>
+      <c r="V42" s="134"/>
+      <c r="W42" s="134"/>
+      <c r="X42" s="134"/>
+      <c r="Y42" s="134"/>
+      <c r="Z42" s="216"/>
     </row>
     <row r="43" customHeight="1" spans="2:26">
-      <c r="B43" s="123" t="s">
+      <c r="B43" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="117" t="s">
+      <c r="C43" s="140" t="s">
         <v>91</v>
       </c>
-      <c r="D43" s="117"/>
-      <c r="E43" s="117"/>
-      <c r="F43" s="117"/>
-      <c r="G43" s="117" t="s">
+      <c r="D43" s="140"/>
+      <c r="E43" s="140"/>
+      <c r="F43" s="140"/>
+      <c r="G43" s="140" t="s">
         <v>92</v>
       </c>
-      <c r="H43" s="111"/>
-      <c r="I43" s="111"/>
-      <c r="J43" s="111"/>
-      <c r="K43" s="111"/>
-      <c r="L43" s="111"/>
-      <c r="M43" s="111"/>
-      <c r="N43" s="111"/>
-      <c r="O43" s="111"/>
-      <c r="P43" s="111"/>
-      <c r="Q43" s="111"/>
-      <c r="R43" s="111"/>
-      <c r="S43" s="111"/>
-      <c r="T43" s="111"/>
-      <c r="U43" s="111"/>
-      <c r="V43" s="111"/>
-      <c r="W43" s="111"/>
-      <c r="X43" s="111"/>
-      <c r="Y43" s="111"/>
-      <c r="Z43" s="111"/>
+      <c r="H43" s="134"/>
+      <c r="I43" s="134"/>
+      <c r="J43" s="134"/>
+      <c r="K43" s="134"/>
+      <c r="L43" s="134"/>
+      <c r="M43" s="134"/>
+      <c r="N43" s="134"/>
+      <c r="O43" s="134"/>
+      <c r="P43" s="134"/>
+      <c r="Q43" s="134"/>
+      <c r="R43" s="134"/>
+      <c r="S43" s="134"/>
+      <c r="T43" s="134"/>
+      <c r="U43" s="134"/>
+      <c r="V43" s="134"/>
+      <c r="W43" s="134"/>
+      <c r="X43" s="134"/>
+      <c r="Y43" s="134"/>
+      <c r="Z43" s="216"/>
     </row>
     <row r="44" customHeight="1" spans="2:26">
-      <c r="B44" s="123" t="s">
+      <c r="B44" s="151" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="117" t="s">
+      <c r="C44" s="142" t="s">
         <v>93</v>
       </c>
-      <c r="D44" s="117"/>
-      <c r="E44" s="117"/>
-      <c r="F44" s="117"/>
-      <c r="G44" s="117" t="s">
+      <c r="D44" s="142"/>
+      <c r="E44" s="142"/>
+      <c r="F44" s="142"/>
+      <c r="G44" s="142" t="s">
         <v>94</v>
       </c>
-      <c r="H44" s="111"/>
-      <c r="I44" s="111"/>
-      <c r="J44" s="111"/>
-      <c r="K44" s="111"/>
-      <c r="L44" s="111"/>
-      <c r="M44" s="111"/>
-      <c r="N44" s="111"/>
-      <c r="O44" s="111"/>
-      <c r="P44" s="111"/>
-      <c r="Q44" s="111"/>
-      <c r="R44" s="111"/>
-      <c r="S44" s="111"/>
-      <c r="T44" s="111"/>
-      <c r="U44" s="111"/>
-      <c r="V44" s="111"/>
-      <c r="W44" s="111"/>
-      <c r="X44" s="111"/>
-      <c r="Y44" s="111"/>
-      <c r="Z44" s="111"/>
+      <c r="H44" s="143"/>
+      <c r="I44" s="143"/>
+      <c r="J44" s="143"/>
+      <c r="K44" s="143"/>
+      <c r="L44" s="143"/>
+      <c r="M44" s="143"/>
+      <c r="N44" s="143"/>
+      <c r="O44" s="143"/>
+      <c r="P44" s="143"/>
+      <c r="Q44" s="143"/>
+      <c r="R44" s="143"/>
+      <c r="S44" s="143"/>
+      <c r="T44" s="143"/>
+      <c r="U44" s="143"/>
+      <c r="V44" s="143"/>
+      <c r="W44" s="143"/>
+      <c r="X44" s="143"/>
+      <c r="Y44" s="143"/>
+      <c r="Z44" s="217"/>
     </row>
     <row r="46" customHeight="1" spans="2:26">
-      <c r="B46" s="121" t="s">
+      <c r="B46" s="148" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="122" t="s">
+      <c r="C46" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="122"/>
-      <c r="E46" s="122"/>
-      <c r="F46" s="122"/>
-      <c r="G46" s="122" t="s">
+      <c r="D46" s="149"/>
+      <c r="E46" s="149"/>
+      <c r="F46" s="149"/>
+      <c r="G46" s="149" t="s">
         <v>48</v>
       </c>
-      <c r="H46" s="122"/>
-      <c r="I46" s="122"/>
-      <c r="J46" s="122"/>
-      <c r="K46" s="122"/>
-      <c r="L46" s="122"/>
-      <c r="M46" s="122"/>
-      <c r="N46" s="122"/>
-      <c r="O46" s="122"/>
-      <c r="P46" s="122"/>
-      <c r="Q46" s="122"/>
-      <c r="R46" s="122"/>
-      <c r="S46" s="122"/>
-      <c r="T46" s="122"/>
-      <c r="U46" s="122"/>
-      <c r="V46" s="122"/>
-      <c r="W46" s="122"/>
-      <c r="X46" s="122"/>
-      <c r="Y46" s="122"/>
-      <c r="Z46" s="122"/>
+      <c r="H46" s="149"/>
+      <c r="I46" s="149"/>
+      <c r="J46" s="149"/>
+      <c r="K46" s="149"/>
+      <c r="L46" s="149"/>
+      <c r="M46" s="149"/>
+      <c r="N46" s="149"/>
+      <c r="O46" s="149"/>
+      <c r="P46" s="149"/>
+      <c r="Q46" s="149"/>
+      <c r="R46" s="149"/>
+      <c r="S46" s="149"/>
+      <c r="T46" s="149"/>
+      <c r="U46" s="149"/>
+      <c r="V46" s="149"/>
+      <c r="W46" s="149"/>
+      <c r="X46" s="149"/>
+      <c r="Y46" s="149"/>
+      <c r="Z46" s="219"/>
     </row>
     <row r="47" customHeight="1" spans="2:26">
-      <c r="B47" s="123" t="s">
+      <c r="B47" s="150" t="s">
         <v>49</v>
       </c>
-      <c r="C47" s="117" t="s">
+      <c r="C47" s="140" t="s">
         <v>95</v>
       </c>
-      <c r="D47" s="117"/>
-      <c r="E47" s="117"/>
-      <c r="F47" s="117"/>
-      <c r="G47" s="117" t="s">
+      <c r="D47" s="140"/>
+      <c r="E47" s="140"/>
+      <c r="F47" s="140"/>
+      <c r="G47" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="H47" s="111"/>
-      <c r="I47" s="111"/>
-      <c r="J47" s="111"/>
-      <c r="K47" s="111"/>
-      <c r="L47" s="111"/>
-      <c r="M47" s="111"/>
-      <c r="N47" s="111"/>
-      <c r="O47" s="111"/>
-      <c r="P47" s="111"/>
-      <c r="Q47" s="111"/>
-      <c r="R47" s="111"/>
-      <c r="S47" s="111"/>
-      <c r="T47" s="111"/>
-      <c r="U47" s="111"/>
-      <c r="V47" s="111"/>
-      <c r="W47" s="111"/>
-      <c r="X47" s="111"/>
-      <c r="Y47" s="111"/>
-      <c r="Z47" s="111"/>
+      <c r="H47" s="134"/>
+      <c r="I47" s="134"/>
+      <c r="J47" s="134"/>
+      <c r="K47" s="134"/>
+      <c r="L47" s="134"/>
+      <c r="M47" s="134"/>
+      <c r="N47" s="134"/>
+      <c r="O47" s="134"/>
+      <c r="P47" s="134"/>
+      <c r="Q47" s="134"/>
+      <c r="R47" s="134"/>
+      <c r="S47" s="134"/>
+      <c r="T47" s="134"/>
+      <c r="U47" s="134"/>
+      <c r="V47" s="134"/>
+      <c r="W47" s="134"/>
+      <c r="X47" s="134"/>
+      <c r="Y47" s="134"/>
+      <c r="Z47" s="216"/>
     </row>
     <row r="48" customHeight="1" spans="2:26">
-      <c r="B48" s="123" t="s">
+      <c r="B48" s="150" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="117" t="s">
+      <c r="C48" s="140" t="s">
         <v>97</v>
       </c>
-      <c r="D48" s="117"/>
-      <c r="E48" s="117"/>
-      <c r="F48" s="117"/>
-      <c r="G48" s="117" t="s">
+      <c r="D48" s="140"/>
+      <c r="E48" s="140"/>
+      <c r="F48" s="140"/>
+      <c r="G48" s="140" t="s">
         <v>98</v>
       </c>
-      <c r="H48" s="111"/>
-      <c r="I48" s="111"/>
-      <c r="J48" s="111"/>
-      <c r="K48" s="111"/>
-      <c r="L48" s="111"/>
-      <c r="M48" s="111"/>
-      <c r="N48" s="111"/>
-      <c r="O48" s="111"/>
-      <c r="P48" s="111"/>
-      <c r="Q48" s="111"/>
-      <c r="R48" s="111"/>
-      <c r="S48" s="111"/>
-      <c r="T48" s="111"/>
-      <c r="U48" s="111"/>
-      <c r="V48" s="111"/>
-      <c r="W48" s="111"/>
-      <c r="X48" s="111"/>
-      <c r="Y48" s="111"/>
-      <c r="Z48" s="111"/>
+      <c r="H48" s="134"/>
+      <c r="I48" s="134"/>
+      <c r="J48" s="134"/>
+      <c r="K48" s="134"/>
+      <c r="L48" s="134"/>
+      <c r="M48" s="134"/>
+      <c r="N48" s="134"/>
+      <c r="O48" s="134"/>
+      <c r="P48" s="134"/>
+      <c r="Q48" s="134"/>
+      <c r="R48" s="134"/>
+      <c r="S48" s="134"/>
+      <c r="T48" s="134"/>
+      <c r="U48" s="134"/>
+      <c r="V48" s="134"/>
+      <c r="W48" s="134"/>
+      <c r="X48" s="134"/>
+      <c r="Y48" s="134"/>
+      <c r="Z48" s="216"/>
     </row>
     <row r="49" customHeight="1" spans="2:26">
-      <c r="B49" s="123" t="s">
+      <c r="B49" s="150" t="s">
         <v>87</v>
       </c>
-      <c r="C49" s="117" t="s">
+      <c r="C49" s="140" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="117"/>
-      <c r="E49" s="117"/>
-      <c r="F49" s="117"/>
-      <c r="G49" s="117" t="s">
+      <c r="D49" s="140"/>
+      <c r="E49" s="140"/>
+      <c r="F49" s="140"/>
+      <c r="G49" s="140" t="s">
         <v>89</v>
       </c>
-      <c r="H49" s="111"/>
-      <c r="I49" s="111"/>
-      <c r="J49" s="111"/>
-      <c r="K49" s="111"/>
-      <c r="L49" s="111"/>
-      <c r="M49" s="111"/>
-      <c r="N49" s="111"/>
-      <c r="O49" s="111"/>
-      <c r="P49" s="111"/>
-      <c r="Q49" s="111"/>
-      <c r="R49" s="111"/>
-      <c r="S49" s="111"/>
-      <c r="T49" s="111"/>
-      <c r="U49" s="111"/>
-      <c r="V49" s="111"/>
-      <c r="W49" s="111"/>
-      <c r="X49" s="111"/>
-      <c r="Y49" s="111"/>
-      <c r="Z49" s="111"/>
+      <c r="H49" s="134"/>
+      <c r="I49" s="134"/>
+      <c r="J49" s="134"/>
+      <c r="K49" s="134"/>
+      <c r="L49" s="134"/>
+      <c r="M49" s="134"/>
+      <c r="N49" s="134"/>
+      <c r="O49" s="134"/>
+      <c r="P49" s="134"/>
+      <c r="Q49" s="134"/>
+      <c r="R49" s="134"/>
+      <c r="S49" s="134"/>
+      <c r="T49" s="134"/>
+      <c r="U49" s="134"/>
+      <c r="V49" s="134"/>
+      <c r="W49" s="134"/>
+      <c r="X49" s="134"/>
+      <c r="Y49" s="134"/>
+      <c r="Z49" s="216"/>
     </row>
     <row r="50" customHeight="1" spans="2:26">
-      <c r="B50" s="123" t="s">
+      <c r="B50" s="150" t="s">
         <v>90</v>
       </c>
-      <c r="C50" s="117" t="s">
+      <c r="C50" s="140" t="s">
         <v>91</v>
       </c>
-      <c r="D50" s="117"/>
-      <c r="E50" s="117"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="117" t="s">
+      <c r="D50" s="140"/>
+      <c r="E50" s="140"/>
+      <c r="F50" s="140"/>
+      <c r="G50" s="140" t="s">
         <v>92</v>
       </c>
-      <c r="H50" s="111"/>
-      <c r="I50" s="111"/>
-      <c r="J50" s="111"/>
-      <c r="K50" s="111"/>
-      <c r="L50" s="111"/>
-      <c r="M50" s="111"/>
-      <c r="N50" s="111"/>
-      <c r="O50" s="111"/>
-      <c r="P50" s="111"/>
-      <c r="Q50" s="111"/>
-      <c r="R50" s="111"/>
-      <c r="S50" s="111"/>
-      <c r="T50" s="111"/>
-      <c r="U50" s="111"/>
-      <c r="V50" s="111"/>
-      <c r="W50" s="111"/>
-      <c r="X50" s="111"/>
-      <c r="Y50" s="111"/>
-      <c r="Z50" s="111"/>
+      <c r="H50" s="134"/>
+      <c r="I50" s="134"/>
+      <c r="J50" s="134"/>
+      <c r="K50" s="134"/>
+      <c r="L50" s="134"/>
+      <c r="M50" s="134"/>
+      <c r="N50" s="134"/>
+      <c r="O50" s="134"/>
+      <c r="P50" s="134"/>
+      <c r="Q50" s="134"/>
+      <c r="R50" s="134"/>
+      <c r="S50" s="134"/>
+      <c r="T50" s="134"/>
+      <c r="U50" s="134"/>
+      <c r="V50" s="134"/>
+      <c r="W50" s="134"/>
+      <c r="X50" s="134"/>
+      <c r="Y50" s="134"/>
+      <c r="Z50" s="216"/>
     </row>
     <row r="51" customHeight="1" spans="2:26">
-      <c r="B51" s="123" t="s">
+      <c r="B51" s="151" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="117" t="s">
+      <c r="C51" s="142" t="s">
         <v>93</v>
       </c>
-      <c r="D51" s="117"/>
-      <c r="E51" s="117"/>
-      <c r="F51" s="117"/>
-      <c r="G51" s="117" t="s">
+      <c r="D51" s="142"/>
+      <c r="E51" s="142"/>
+      <c r="F51" s="142"/>
+      <c r="G51" s="142" t="s">
         <v>94</v>
       </c>
-      <c r="H51" s="111"/>
-      <c r="I51" s="111"/>
-      <c r="J51" s="111"/>
-      <c r="K51" s="111"/>
-      <c r="L51" s="111"/>
-      <c r="M51" s="111"/>
-      <c r="N51" s="111"/>
-      <c r="O51" s="111"/>
-      <c r="P51" s="111"/>
-      <c r="Q51" s="111"/>
-      <c r="R51" s="111"/>
-      <c r="S51" s="111"/>
-      <c r="T51" s="111"/>
-      <c r="U51" s="111"/>
-      <c r="V51" s="111"/>
-      <c r="W51" s="111"/>
-      <c r="X51" s="111"/>
-      <c r="Y51" s="111"/>
-      <c r="Z51" s="111"/>
+      <c r="H51" s="143"/>
+      <c r="I51" s="143"/>
+      <c r="J51" s="143"/>
+      <c r="K51" s="143"/>
+      <c r="L51" s="143"/>
+      <c r="M51" s="143"/>
+      <c r="N51" s="143"/>
+      <c r="O51" s="143"/>
+      <c r="P51" s="143"/>
+      <c r="Q51" s="143"/>
+      <c r="R51" s="143"/>
+      <c r="S51" s="143"/>
+      <c r="T51" s="143"/>
+      <c r="U51" s="143"/>
+      <c r="V51" s="143"/>
+      <c r="W51" s="143"/>
+      <c r="X51" s="143"/>
+      <c r="Y51" s="143"/>
+      <c r="Z51" s="217"/>
     </row>
     <row r="53" customHeight="1" spans="2:26">
-      <c r="B53" s="124" t="s">
+      <c r="B53" s="152" t="s">
         <v>46</v>
       </c>
-      <c r="C53" s="125" t="s">
+      <c r="C53" s="153" t="s">
         <v>32</v>
       </c>
-      <c r="D53" s="125"/>
-      <c r="E53" s="125"/>
-      <c r="F53" s="125"/>
-      <c r="G53" s="125" t="s">
+      <c r="D53" s="153"/>
+      <c r="E53" s="153"/>
+      <c r="F53" s="153"/>
+      <c r="G53" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="H53" s="125"/>
-      <c r="I53" s="125"/>
-      <c r="J53" s="125"/>
-      <c r="K53" s="125"/>
-      <c r="L53" s="125"/>
-      <c r="M53" s="125"/>
-      <c r="N53" s="125"/>
-      <c r="O53" s="125"/>
-      <c r="P53" s="125"/>
-      <c r="Q53" s="125"/>
-      <c r="R53" s="125"/>
-      <c r="S53" s="125"/>
-      <c r="T53" s="125"/>
-      <c r="U53" s="125"/>
-      <c r="V53" s="125"/>
-      <c r="W53" s="125"/>
-      <c r="X53" s="125"/>
-      <c r="Y53" s="125"/>
-      <c r="Z53" s="125"/>
+      <c r="H53" s="153"/>
+      <c r="I53" s="153"/>
+      <c r="J53" s="153"/>
+      <c r="K53" s="153"/>
+      <c r="L53" s="153"/>
+      <c r="M53" s="153"/>
+      <c r="N53" s="153"/>
+      <c r="O53" s="153"/>
+      <c r="P53" s="153"/>
+      <c r="Q53" s="153"/>
+      <c r="R53" s="153"/>
+      <c r="S53" s="153"/>
+      <c r="T53" s="153"/>
+      <c r="U53" s="153"/>
+      <c r="V53" s="153"/>
+      <c r="W53" s="153"/>
+      <c r="X53" s="153"/>
+      <c r="Y53" s="153"/>
+      <c r="Z53" s="220"/>
     </row>
     <row r="54" customHeight="1" spans="2:26">
-      <c r="B54" s="126" t="s">
+      <c r="B54" s="154" t="s">
         <v>49</v>
       </c>
-      <c r="C54" s="127" t="s">
+      <c r="C54" s="155" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="127"/>
-      <c r="E54" s="127"/>
-      <c r="F54" s="127"/>
-      <c r="G54" s="117" t="s">
+      <c r="D54" s="155"/>
+      <c r="E54" s="155"/>
+      <c r="F54" s="155"/>
+      <c r="G54" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="H54" s="111"/>
-      <c r="I54" s="111"/>
-      <c r="J54" s="111"/>
-      <c r="K54" s="111"/>
-      <c r="L54" s="111"/>
-      <c r="M54" s="111"/>
-      <c r="N54" s="111"/>
-      <c r="O54" s="111"/>
-      <c r="P54" s="111"/>
-      <c r="Q54" s="111"/>
-      <c r="R54" s="111"/>
-      <c r="S54" s="111"/>
-      <c r="T54" s="111"/>
-      <c r="U54" s="111"/>
-      <c r="V54" s="111"/>
-      <c r="W54" s="111"/>
-      <c r="X54" s="111"/>
-      <c r="Y54" s="111"/>
-      <c r="Z54" s="111"/>
+      <c r="H54" s="134"/>
+      <c r="I54" s="134"/>
+      <c r="J54" s="134"/>
+      <c r="K54" s="134"/>
+      <c r="L54" s="134"/>
+      <c r="M54" s="134"/>
+      <c r="N54" s="134"/>
+      <c r="O54" s="134"/>
+      <c r="P54" s="134"/>
+      <c r="Q54" s="134"/>
+      <c r="R54" s="134"/>
+      <c r="S54" s="134"/>
+      <c r="T54" s="134"/>
+      <c r="U54" s="134"/>
+      <c r="V54" s="134"/>
+      <c r="W54" s="134"/>
+      <c r="X54" s="134"/>
+      <c r="Y54" s="134"/>
+      <c r="Z54" s="216"/>
     </row>
     <row r="55" customHeight="1" spans="2:26">
-      <c r="B55" s="126" t="s">
+      <c r="B55" s="154" t="s">
         <v>52</v>
       </c>
-      <c r="C55" s="127" t="s">
+      <c r="C55" s="155" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="127"/>
-      <c r="E55" s="127"/>
-      <c r="F55" s="127"/>
-      <c r="G55" s="117" t="s">
+      <c r="D55" s="155"/>
+      <c r="E55" s="155"/>
+      <c r="F55" s="155"/>
+      <c r="G55" s="140" t="s">
         <v>101</v>
       </c>
-      <c r="H55" s="111"/>
-      <c r="I55" s="111"/>
-      <c r="J55" s="111"/>
-      <c r="K55" s="111"/>
-      <c r="L55" s="111"/>
-      <c r="M55" s="111"/>
-      <c r="N55" s="111"/>
-      <c r="O55" s="111"/>
-      <c r="P55" s="111"/>
-      <c r="Q55" s="111"/>
-      <c r="R55" s="111"/>
-      <c r="S55" s="111"/>
-      <c r="T55" s="111"/>
-      <c r="U55" s="111"/>
-      <c r="V55" s="111"/>
-      <c r="W55" s="111"/>
-      <c r="X55" s="111"/>
-      <c r="Y55" s="111"/>
-      <c r="Z55" s="111"/>
+      <c r="H55" s="134"/>
+      <c r="I55" s="134"/>
+      <c r="J55" s="134"/>
+      <c r="K55" s="134"/>
+      <c r="L55" s="134"/>
+      <c r="M55" s="134"/>
+      <c r="N55" s="134"/>
+      <c r="O55" s="134"/>
+      <c r="P55" s="134"/>
+      <c r="Q55" s="134"/>
+      <c r="R55" s="134"/>
+      <c r="S55" s="134"/>
+      <c r="T55" s="134"/>
+      <c r="U55" s="134"/>
+      <c r="V55" s="134"/>
+      <c r="W55" s="134"/>
+      <c r="X55" s="134"/>
+      <c r="Y55" s="134"/>
+      <c r="Z55" s="216"/>
     </row>
     <row r="56" customHeight="1" spans="2:26">
-      <c r="B56" s="126" t="s">
+      <c r="B56" s="154" t="s">
         <v>102</v>
       </c>
-      <c r="C56" s="117" t="s">
+      <c r="C56" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="D56" s="117"/>
-      <c r="E56" s="117"/>
-      <c r="F56" s="117"/>
-      <c r="G56" s="117" t="s">
+      <c r="D56" s="140"/>
+      <c r="E56" s="140"/>
+      <c r="F56" s="140"/>
+      <c r="G56" s="140" t="s">
         <v>103</v>
       </c>
-      <c r="H56" s="111"/>
-      <c r="I56" s="111"/>
-      <c r="J56" s="111"/>
-      <c r="K56" s="111"/>
-      <c r="L56" s="111"/>
-      <c r="M56" s="111"/>
-      <c r="N56" s="111"/>
-      <c r="O56" s="111"/>
-      <c r="P56" s="111"/>
-      <c r="Q56" s="111"/>
-      <c r="R56" s="111"/>
-      <c r="S56" s="111"/>
-      <c r="T56" s="111"/>
-      <c r="U56" s="111"/>
-      <c r="V56" s="111"/>
-      <c r="W56" s="111"/>
-      <c r="X56" s="111"/>
-      <c r="Y56" s="111"/>
-      <c r="Z56" s="111"/>
+      <c r="H56" s="134"/>
+      <c r="I56" s="134"/>
+      <c r="J56" s="134"/>
+      <c r="K56" s="134"/>
+      <c r="L56" s="134"/>
+      <c r="M56" s="134"/>
+      <c r="N56" s="134"/>
+      <c r="O56" s="134"/>
+      <c r="P56" s="134"/>
+      <c r="Q56" s="134"/>
+      <c r="R56" s="134"/>
+      <c r="S56" s="134"/>
+      <c r="T56" s="134"/>
+      <c r="U56" s="134"/>
+      <c r="V56" s="134"/>
+      <c r="W56" s="134"/>
+      <c r="X56" s="134"/>
+      <c r="Y56" s="134"/>
+      <c r="Z56" s="216"/>
     </row>
     <row r="57" customHeight="1" spans="2:26">
-      <c r="B57" s="126" t="s">
+      <c r="B57" s="154" t="s">
         <v>87</v>
       </c>
-      <c r="C57" s="117" t="s">
+      <c r="C57" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="D57" s="117"/>
-      <c r="E57" s="117"/>
-      <c r="F57" s="117"/>
-      <c r="G57" s="117" t="s">
+      <c r="D57" s="140"/>
+      <c r="E57" s="140"/>
+      <c r="F57" s="140"/>
+      <c r="G57" s="140" t="s">
         <v>105</v>
       </c>
-      <c r="H57" s="111"/>
-      <c r="I57" s="111"/>
-      <c r="J57" s="111"/>
-      <c r="K57" s="111"/>
-      <c r="L57" s="111"/>
-      <c r="M57" s="111"/>
-      <c r="N57" s="111"/>
-      <c r="O57" s="111"/>
-      <c r="P57" s="111"/>
-      <c r="Q57" s="111"/>
-      <c r="R57" s="111"/>
-      <c r="S57" s="111"/>
-      <c r="T57" s="111"/>
-      <c r="U57" s="111"/>
-      <c r="V57" s="111"/>
-      <c r="W57" s="111"/>
-      <c r="X57" s="111"/>
-      <c r="Y57" s="111"/>
-      <c r="Z57" s="111"/>
+      <c r="H57" s="134"/>
+      <c r="I57" s="134"/>
+      <c r="J57" s="134"/>
+      <c r="K57" s="134"/>
+      <c r="L57" s="134"/>
+      <c r="M57" s="134"/>
+      <c r="N57" s="134"/>
+      <c r="O57" s="134"/>
+      <c r="P57" s="134"/>
+      <c r="Q57" s="134"/>
+      <c r="R57" s="134"/>
+      <c r="S57" s="134"/>
+      <c r="T57" s="134"/>
+      <c r="U57" s="134"/>
+      <c r="V57" s="134"/>
+      <c r="W57" s="134"/>
+      <c r="X57" s="134"/>
+      <c r="Y57" s="134"/>
+      <c r="Z57" s="216"/>
     </row>
     <row r="58" customHeight="1" spans="2:26">
-      <c r="B58" s="126" t="s">
+      <c r="B58" s="154" t="s">
         <v>106</v>
       </c>
-      <c r="C58" s="117" t="s">
+      <c r="C58" s="140" t="s">
         <v>107</v>
       </c>
-      <c r="D58" s="117"/>
-      <c r="E58" s="117"/>
-      <c r="F58" s="117"/>
-      <c r="G58" s="117" t="s">
+      <c r="D58" s="140"/>
+      <c r="E58" s="140"/>
+      <c r="F58" s="140"/>
+      <c r="G58" s="140" t="s">
         <v>108</v>
       </c>
-      <c r="H58" s="111"/>
-      <c r="I58" s="111"/>
-      <c r="J58" s="111"/>
-      <c r="K58" s="111"/>
-      <c r="L58" s="111"/>
-      <c r="M58" s="111"/>
-      <c r="N58" s="111"/>
-      <c r="O58" s="111"/>
-      <c r="P58" s="111"/>
-      <c r="Q58" s="111"/>
-      <c r="R58" s="111"/>
-      <c r="S58" s="111"/>
-      <c r="T58" s="111"/>
-      <c r="U58" s="111"/>
-      <c r="V58" s="111"/>
-      <c r="W58" s="111"/>
-      <c r="X58" s="111"/>
-      <c r="Y58" s="111"/>
-      <c r="Z58" s="111"/>
+      <c r="H58" s="134"/>
+      <c r="I58" s="134"/>
+      <c r="J58" s="134"/>
+      <c r="K58" s="134"/>
+      <c r="L58" s="134"/>
+      <c r="M58" s="134"/>
+      <c r="N58" s="134"/>
+      <c r="O58" s="134"/>
+      <c r="P58" s="134"/>
+      <c r="Q58" s="134"/>
+      <c r="R58" s="134"/>
+      <c r="S58" s="134"/>
+      <c r="T58" s="134"/>
+      <c r="U58" s="134"/>
+      <c r="V58" s="134"/>
+      <c r="W58" s="134"/>
+      <c r="X58" s="134"/>
+      <c r="Y58" s="134"/>
+      <c r="Z58" s="216"/>
     </row>
     <row r="59" customHeight="1" spans="2:26">
-      <c r="B59" s="126" t="s">
+      <c r="B59" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="117" t="s">
+      <c r="C59" s="140" t="s">
         <v>109</v>
       </c>
-      <c r="D59" s="117"/>
-      <c r="E59" s="117"/>
-      <c r="F59" s="117"/>
-      <c r="G59" s="117" t="s">
+      <c r="D59" s="140"/>
+      <c r="E59" s="140"/>
+      <c r="F59" s="140"/>
+      <c r="G59" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="H59" s="111"/>
-      <c r="I59" s="111"/>
-      <c r="J59" s="111"/>
-      <c r="K59" s="111"/>
-      <c r="L59" s="111"/>
-      <c r="M59" s="111"/>
-      <c r="N59" s="111"/>
-      <c r="O59" s="111"/>
-      <c r="P59" s="111"/>
-      <c r="Q59" s="111"/>
-      <c r="R59" s="111"/>
-      <c r="S59" s="111"/>
-      <c r="T59" s="111"/>
-      <c r="U59" s="111"/>
-      <c r="V59" s="111"/>
-      <c r="W59" s="111"/>
-      <c r="X59" s="111"/>
-      <c r="Y59" s="111"/>
-      <c r="Z59" s="111"/>
+      <c r="H59" s="134"/>
+      <c r="I59" s="134"/>
+      <c r="J59" s="134"/>
+      <c r="K59" s="134"/>
+      <c r="L59" s="134"/>
+      <c r="M59" s="134"/>
+      <c r="N59" s="134"/>
+      <c r="O59" s="134"/>
+      <c r="P59" s="134"/>
+      <c r="Q59" s="134"/>
+      <c r="R59" s="134"/>
+      <c r="S59" s="134"/>
+      <c r="T59" s="134"/>
+      <c r="U59" s="134"/>
+      <c r="V59" s="134"/>
+      <c r="W59" s="134"/>
+      <c r="X59" s="134"/>
+      <c r="Y59" s="134"/>
+      <c r="Z59" s="216"/>
     </row>
     <row r="60" customHeight="1" spans="2:26">
-      <c r="B60" s="126" t="s">
+      <c r="B60" s="154" t="s">
         <v>62</v>
       </c>
-      <c r="C60" s="117" t="s">
+      <c r="C60" s="140" t="s">
         <v>66</v>
       </c>
-      <c r="D60" s="117"/>
-      <c r="E60" s="117"/>
-      <c r="F60" s="117"/>
-      <c r="G60" s="117" t="s">
+      <c r="D60" s="140"/>
+      <c r="E60" s="140"/>
+      <c r="F60" s="140"/>
+      <c r="G60" s="140" t="s">
         <v>110</v>
       </c>
-      <c r="H60" s="111"/>
-      <c r="I60" s="111"/>
-      <c r="J60" s="111"/>
-      <c r="K60" s="111"/>
-      <c r="L60" s="111"/>
-      <c r="M60" s="111"/>
-      <c r="N60" s="111"/>
-      <c r="O60" s="111"/>
-      <c r="P60" s="111"/>
-      <c r="Q60" s="111"/>
-      <c r="R60" s="111"/>
-      <c r="S60" s="111"/>
-      <c r="T60" s="111"/>
-      <c r="U60" s="111"/>
-      <c r="V60" s="111"/>
-      <c r="W60" s="111"/>
-      <c r="X60" s="111"/>
-      <c r="Y60" s="111"/>
-      <c r="Z60" s="111"/>
+      <c r="H60" s="134"/>
+      <c r="I60" s="134"/>
+      <c r="J60" s="134"/>
+      <c r="K60" s="134"/>
+      <c r="L60" s="134"/>
+      <c r="M60" s="134"/>
+      <c r="N60" s="134"/>
+      <c r="O60" s="134"/>
+      <c r="P60" s="134"/>
+      <c r="Q60" s="134"/>
+      <c r="R60" s="134"/>
+      <c r="S60" s="134"/>
+      <c r="T60" s="134"/>
+      <c r="U60" s="134"/>
+      <c r="V60" s="134"/>
+      <c r="W60" s="134"/>
+      <c r="X60" s="134"/>
+      <c r="Y60" s="134"/>
+      <c r="Z60" s="216"/>
     </row>
     <row r="61" customHeight="1" spans="2:26">
-      <c r="B61" s="126" t="s">
+      <c r="B61" s="156" t="s">
         <v>81</v>
       </c>
-      <c r="C61" s="117" t="s">
+      <c r="C61" s="142" t="s">
         <v>44</v>
       </c>
-      <c r="D61" s="117"/>
-      <c r="E61" s="117"/>
-      <c r="F61" s="117"/>
-      <c r="G61" s="117" t="s">
+      <c r="D61" s="142"/>
+      <c r="E61" s="142"/>
+      <c r="F61" s="142"/>
+      <c r="G61" s="142" t="s">
         <v>111</v>
       </c>
-      <c r="H61" s="111"/>
-      <c r="I61" s="111"/>
-      <c r="J61" s="111"/>
-      <c r="K61" s="111"/>
-      <c r="L61" s="111"/>
-      <c r="M61" s="111"/>
-      <c r="N61" s="111"/>
-      <c r="O61" s="111"/>
-      <c r="P61" s="111"/>
-      <c r="Q61" s="111"/>
-      <c r="R61" s="111"/>
-      <c r="S61" s="111"/>
-      <c r="T61" s="111"/>
-      <c r="U61" s="111"/>
-      <c r="V61" s="111"/>
-      <c r="W61" s="111"/>
-      <c r="X61" s="111"/>
-      <c r="Y61" s="111"/>
-      <c r="Z61" s="111"/>
+      <c r="H61" s="143"/>
+      <c r="I61" s="143"/>
+      <c r="J61" s="143"/>
+      <c r="K61" s="143"/>
+      <c r="L61" s="143"/>
+      <c r="M61" s="143"/>
+      <c r="N61" s="143"/>
+      <c r="O61" s="143"/>
+      <c r="P61" s="143"/>
+      <c r="Q61" s="143"/>
+      <c r="R61" s="143"/>
+      <c r="S61" s="143"/>
+      <c r="T61" s="143"/>
+      <c r="U61" s="143"/>
+      <c r="V61" s="143"/>
+      <c r="W61" s="143"/>
+      <c r="X61" s="143"/>
+      <c r="Y61" s="143"/>
+      <c r="Z61" s="217"/>
     </row>
   </sheetData>
   <mergeCells count="93">
@@ -5944,8 +6184,8 @@
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A18:F19"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.298611111111111" footer="0.298611111111111"/>
+  <pageSetup paperSize="9" scale="63" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
     <ignoredError sqref="B58:B60 B28:B32 B24:B26 B47 B54:B56" numberStoredAsText="1"/>
@@ -5955,2029 +6195,2031 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:W33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.625" style="46" customWidth="1"/>
-    <col min="2" max="15" width="6.625" style="46" customWidth="1"/>
-    <col min="16" max="16" width="9" style="46"/>
-    <col min="17" max="17" width="15.625" style="46" customWidth="1"/>
-    <col min="18" max="18" width="20.625" style="46" customWidth="1"/>
-    <col min="19" max="19" width="9" style="46"/>
-    <col min="20" max="20" width="39.625" style="46" customWidth="1"/>
-    <col min="21" max="21" width="9.5" style="46" customWidth="1"/>
-    <col min="22" max="22" width="20.625" style="46" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="46"/>
+    <col min="1" max="1" width="15.625" style="56" customWidth="1"/>
+    <col min="2" max="15" width="6.625" style="56" customWidth="1"/>
+    <col min="16" max="16" width="9" style="56"/>
+    <col min="17" max="17" width="15.625" style="56" customWidth="1"/>
+    <col min="18" max="18" width="20.625" style="56" customWidth="1"/>
+    <col min="19" max="19" width="9" style="56"/>
+    <col min="20" max="20" width="39.625" style="56" customWidth="1"/>
+    <col min="21" max="21" width="9.5" style="56" customWidth="1"/>
+    <col min="22" max="22" width="20.625" style="56" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="56"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="48">
+      <c r="B1" s="58">
         <v>10</v>
       </c>
-      <c r="C1" s="48">
+      <c r="C1" s="58">
         <v>20</v>
       </c>
-      <c r="D1" s="48">
+      <c r="D1" s="58">
         <v>30</v>
       </c>
-      <c r="E1" s="48">
+      <c r="E1" s="58">
         <v>40</v>
       </c>
-      <c r="F1" s="49">
+      <c r="F1" s="59">
         <v>50</v>
       </c>
-      <c r="G1" s="48">
+      <c r="G1" s="58">
         <v>60</v>
       </c>
-      <c r="H1" s="49">
+      <c r="H1" s="59">
         <v>70</v>
       </c>
-      <c r="I1" s="48">
+      <c r="I1" s="58">
         <v>80</v>
       </c>
-      <c r="J1" s="48">
+      <c r="J1" s="58">
         <v>90</v>
       </c>
-      <c r="K1" s="48">
+      <c r="K1" s="58">
         <v>100</v>
       </c>
-      <c r="L1" s="48">
+      <c r="L1" s="58">
         <v>110</v>
       </c>
-      <c r="M1" s="48">
+      <c r="M1" s="58">
         <v>120</v>
       </c>
-      <c r="N1" s="48">
+      <c r="N1" s="58">
         <v>130</v>
       </c>
-      <c r="O1" s="56">
+      <c r="O1" s="70">
         <v>140</v>
       </c>
-      <c r="Q1" s="57" t="s">
+      <c r="Q1" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="R1" s="57" t="s">
+      <c r="R1" s="76" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:18">
-      <c r="A2" s="50"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="56"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="71"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="78"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:18">
-      <c r="A3" s="51">
+      <c r="A3" s="63">
         <v>0</v>
       </c>
-      <c r="B3" s="52">
+      <c r="B3" s="64">
         <f>ROUND($A3*B$1,0)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="52">
+      <c r="C3" s="64">
         <f t="shared" ref="C3:O3" si="0">ROUND($A3*C$1,0)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="52">
+      <c r="D3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E3" s="52">
+      <c r="E3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F3" s="52">
+      <c r="F3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G3" s="52">
+      <c r="G3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H3" s="52">
+      <c r="H3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J3" s="52">
+      <c r="J3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K3" s="52">
+      <c r="K3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L3" s="52">
+      <c r="L3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M3" s="52">
+      <c r="M3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N3" s="52">
+      <c r="N3" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O3" s="52">
+      <c r="O3" s="72">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q3" s="58" t="s">
+      <c r="Q3" s="79" t="s">
         <v>115</v>
       </c>
-      <c r="R3" s="59" t="s">
+      <c r="R3" s="80" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:18">
-      <c r="A4" s="53">
+      <c r="A4" s="65">
         <v>0.01</v>
       </c>
-      <c r="B4" s="54">
+      <c r="B4" s="66">
         <f>ROUND($A4*B$1,0)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="54">
+      <c r="C4" s="66">
         <f>ROUND($A4*C$1,0)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="54">
+      <c r="D4" s="66">
         <f>ROUND($A4*D$1,0)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="66">
         <f>ROUND($A4*E$1,0)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="54">
+      <c r="F4" s="66">
         <f>ROUND($A4*F$1,0)</f>
         <v>1</v>
       </c>
-      <c r="G4" s="54">
+      <c r="G4" s="66">
         <f>ROUND($A4*G$1,0)</f>
         <v>1</v>
       </c>
-      <c r="H4" s="54">
+      <c r="H4" s="66">
         <f>ROUND($A4*H$1,0)</f>
         <v>1</v>
       </c>
-      <c r="I4" s="54">
+      <c r="I4" s="66">
         <f>ROUND($A4*I$1,0)</f>
         <v>1</v>
       </c>
-      <c r="J4" s="54">
+      <c r="J4" s="66">
         <f>ROUND($A4*J$1,0)</f>
         <v>1</v>
       </c>
-      <c r="K4" s="54">
+      <c r="K4" s="66">
         <f>ROUND($A4*K$1,0)</f>
         <v>1</v>
       </c>
-      <c r="L4" s="54">
+      <c r="L4" s="66">
         <f>ROUND($A4*L$1,0)</f>
         <v>1</v>
       </c>
-      <c r="M4" s="54">
+      <c r="M4" s="66">
         <f>ROUND($A4*M$1,0)</f>
         <v>1</v>
       </c>
-      <c r="N4" s="54">
+      <c r="N4" s="66">
         <f>ROUND($A4*N$1,0)</f>
         <v>1</v>
       </c>
-      <c r="O4" s="54">
+      <c r="O4" s="73">
         <f>ROUND($A4*O$1,0)</f>
         <v>1</v>
       </c>
-      <c r="Q4" s="58" t="s">
+      <c r="Q4" s="79" t="s">
         <v>117</v>
       </c>
-      <c r="R4" s="59" t="s">
+      <c r="R4" s="80" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:18">
-      <c r="A5" s="55">
+      <c r="A5" s="67">
         <v>0.02</v>
       </c>
-      <c r="B5" s="52">
+      <c r="B5" s="64">
         <f t="shared" ref="B5:B33" si="1">ROUND($A5*B$1,0)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="52">
+      <c r="C5" s="64">
         <f t="shared" ref="C5:C33" si="2">ROUND($A5*C$1,0)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="52">
+      <c r="D5" s="64">
         <f t="shared" ref="D5:D33" si="3">ROUND($A5*D$1,0)</f>
         <v>1</v>
       </c>
-      <c r="E5" s="52">
+      <c r="E5" s="64">
         <f t="shared" ref="E5:E33" si="4">ROUND($A5*E$1,0)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="52">
+      <c r="F5" s="64">
         <f t="shared" ref="F5:F33" si="5">ROUND($A5*F$1,0)</f>
         <v>1</v>
       </c>
-      <c r="G5" s="52">
+      <c r="G5" s="64">
         <f t="shared" ref="G5:G33" si="6">ROUND($A5*G$1,0)</f>
         <v>1</v>
       </c>
-      <c r="H5" s="52">
+      <c r="H5" s="64">
         <f t="shared" ref="H5:H33" si="7">ROUND($A5*H$1,0)</f>
         <v>1</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="64">
         <f t="shared" ref="I5:I33" si="8">ROUND($A5*I$1,0)</f>
         <v>2</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="64">
         <f t="shared" ref="J5:J33" si="9">ROUND($A5*J$1,0)</f>
         <v>2</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="64">
         <f t="shared" ref="K5:K33" si="10">ROUND($A5*K$1,0)</f>
         <v>2</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="64">
         <f t="shared" ref="L5:L33" si="11">ROUND($A5*L$1,0)</f>
         <v>2</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="64">
         <f t="shared" ref="M5:M33" si="12">ROUND($A5*M$1,0)</f>
         <v>2</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="64">
         <f t="shared" ref="N5:N33" si="13">ROUND($A5*N$1,0)</f>
         <v>3</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="72">
         <f t="shared" ref="O5:O33" si="14">ROUND($A5*O$1,0)</f>
         <v>3</v>
       </c>
-      <c r="Q5" s="58" t="s">
+      <c r="Q5" s="79" t="s">
         <v>119</v>
       </c>
-      <c r="R5" s="59" t="s">
+      <c r="R5" s="80" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:18">
-      <c r="A6" s="53">
+      <c r="A6" s="65">
         <v>0.03</v>
       </c>
-      <c r="B6" s="54">
+      <c r="B6" s="66">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="66">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="66">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="66">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="66">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G6" s="54">
+      <c r="G6" s="66">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="H6" s="54">
+      <c r="H6" s="66">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="66">
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="66">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="66">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="66">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="66">
         <f t="shared" si="12"/>
         <v>4</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="66">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="73">
         <f t="shared" si="14"/>
         <v>4</v>
       </c>
-      <c r="Q6" s="58" t="s">
+      <c r="Q6" s="79" t="s">
         <v>121</v>
       </c>
-      <c r="R6" s="59" t="s">
+      <c r="R6" s="80" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:18">
-      <c r="A7" s="55">
+      <c r="A7" s="67">
         <v>0.04</v>
       </c>
-      <c r="B7" s="52">
+      <c r="B7" s="64">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C7" s="52">
+      <c r="C7" s="64">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="64">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="E7" s="52">
+      <c r="E7" s="64">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="64">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="64">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="64">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="64">
         <f t="shared" si="8"/>
         <v>3</v>
       </c>
-      <c r="J7" s="52">
+      <c r="J7" s="64">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="K7" s="52">
+      <c r="K7" s="64">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="L7" s="52">
+      <c r="L7" s="64">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
-      <c r="M7" s="52">
+      <c r="M7" s="64">
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="N7" s="52">
+      <c r="N7" s="64">
         <f t="shared" si="13"/>
         <v>5</v>
       </c>
-      <c r="O7" s="52">
+      <c r="O7" s="72">
         <f t="shared" si="14"/>
         <v>6</v>
       </c>
-      <c r="Q7" s="58" t="s">
+      <c r="Q7" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="R7" s="59" t="s">
+      <c r="R7" s="80" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:18">
-      <c r="A8" s="53">
+      <c r="A8" s="65">
         <v>0.05</v>
       </c>
-      <c r="B8" s="54">
+      <c r="B8" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C8" s="54">
+      <c r="C8" s="66">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="66">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="66">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="66">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="66">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="H8" s="54">
+      <c r="H8" s="66">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="66">
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="J8" s="54">
+      <c r="J8" s="66">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="K8" s="54">
+      <c r="K8" s="66">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="L8" s="54">
+      <c r="L8" s="66">
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
-      <c r="M8" s="54">
+      <c r="M8" s="66">
         <f t="shared" si="12"/>
         <v>6</v>
       </c>
-      <c r="N8" s="54">
+      <c r="N8" s="66">
         <f t="shared" si="13"/>
         <v>7</v>
       </c>
-      <c r="O8" s="54">
+      <c r="O8" s="73">
         <f t="shared" si="14"/>
         <v>7</v>
       </c>
-      <c r="Q8" s="58" t="s">
+      <c r="Q8" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="R8" s="59" t="s">
+      <c r="R8" s="80" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:18">
-      <c r="A9" s="55">
+      <c r="A9" s="67">
         <v>0.06</v>
       </c>
-      <c r="B9" s="52">
+      <c r="B9" s="64">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C9" s="52">
+      <c r="C9" s="64">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D9" s="52">
+      <c r="D9" s="64">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E9" s="52">
+      <c r="E9" s="64">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F9" s="52">
+      <c r="F9" s="64">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="G9" s="52">
+      <c r="G9" s="64">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="H9" s="52">
+      <c r="H9" s="64">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="64">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="J9" s="52">
+      <c r="J9" s="64">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="K9" s="52">
+      <c r="K9" s="64">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="L9" s="52">
+      <c r="L9" s="64">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
-      <c r="M9" s="52">
+      <c r="M9" s="64">
         <f t="shared" si="12"/>
         <v>7</v>
       </c>
-      <c r="N9" s="52">
+      <c r="N9" s="64">
         <f t="shared" si="13"/>
         <v>8</v>
       </c>
-      <c r="O9" s="52">
+      <c r="O9" s="72">
         <f t="shared" si="14"/>
         <v>8</v>
       </c>
-      <c r="Q9" s="58" t="s">
+      <c r="Q9" s="79" t="s">
         <v>127</v>
       </c>
-      <c r="R9" s="59" t="s">
+      <c r="R9" s="80" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:18">
-      <c r="A10" s="53">
+      <c r="A10" s="65">
         <v>0.07</v>
       </c>
-      <c r="B10" s="54">
+      <c r="B10" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C10" s="54">
+      <c r="C10" s="66">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D10" s="54">
+      <c r="D10" s="66">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="66">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F10" s="54">
+      <c r="F10" s="66">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G10" s="54">
+      <c r="G10" s="66">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="H10" s="54">
+      <c r="H10" s="66">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="I10" s="54">
+      <c r="I10" s="66">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="J10" s="54">
+      <c r="J10" s="66">
         <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="K10" s="54">
+      <c r="K10" s="66">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="L10" s="54">
+      <c r="L10" s="66">
         <f t="shared" si="11"/>
         <v>8</v>
       </c>
-      <c r="M10" s="54">
+      <c r="M10" s="66">
         <f t="shared" si="12"/>
         <v>8</v>
       </c>
-      <c r="N10" s="54">
+      <c r="N10" s="66">
         <f t="shared" si="13"/>
         <v>9</v>
       </c>
-      <c r="O10" s="54">
+      <c r="O10" s="73">
         <f t="shared" si="14"/>
         <v>10</v>
       </c>
-      <c r="Q10" s="58" t="s">
+      <c r="Q10" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="R10" s="59" t="s">
+      <c r="R10" s="82" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:15">
-      <c r="A11" s="55">
+      <c r="A11" s="67">
         <v>0.08</v>
       </c>
-      <c r="B11" s="52">
+      <c r="B11" s="64">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C11" s="52">
+      <c r="C11" s="64">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="64">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="64">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="F11" s="52">
+      <c r="F11" s="64">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="G11" s="52">
+      <c r="G11" s="64">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="H11" s="52">
+      <c r="H11" s="64">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11" s="64">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="J11" s="52">
+      <c r="J11" s="64">
         <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="K11" s="52">
+      <c r="K11" s="64">
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
-      <c r="L11" s="52">
+      <c r="L11" s="64">
         <f t="shared" si="11"/>
         <v>9</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11" s="64">
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="N11" s="52">
+      <c r="N11" s="64">
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="O11" s="52">
+      <c r="O11" s="72">
         <f t="shared" si="14"/>
         <v>11</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:15">
-      <c r="A12" s="53">
+      <c r="A12" s="65">
         <v>0.09</v>
       </c>
-      <c r="B12" s="54">
+      <c r="B12" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="66">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D12" s="54">
+      <c r="D12" s="66">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E12" s="54">
+      <c r="E12" s="66">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F12" s="54">
+      <c r="F12" s="66">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="G12" s="54">
+      <c r="G12" s="66">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="H12" s="54">
+      <c r="H12" s="66">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
-      <c r="I12" s="54">
+      <c r="I12" s="66">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="J12" s="54">
+      <c r="J12" s="66">
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="K12" s="54">
+      <c r="K12" s="66">
         <f t="shared" si="10"/>
         <v>9</v>
       </c>
-      <c r="L12" s="54">
+      <c r="L12" s="66">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
-      <c r="M12" s="54">
+      <c r="M12" s="66">
         <f t="shared" si="12"/>
         <v>11</v>
       </c>
-      <c r="N12" s="54">
+      <c r="N12" s="66">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
-      <c r="O12" s="54">
+      <c r="O12" s="73">
         <f t="shared" si="14"/>
         <v>13</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:15">
-      <c r="A13" s="55">
+      <c r="A13" s="67">
         <v>0.1</v>
       </c>
-      <c r="B13" s="52">
+      <c r="B13" s="64">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C13" s="52">
+      <c r="C13" s="64">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D13" s="52">
+      <c r="D13" s="64">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E13" s="52">
+      <c r="E13" s="64">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F13" s="52">
+      <c r="F13" s="64">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="G13" s="52">
+      <c r="G13" s="64">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="H13" s="52">
+      <c r="H13" s="64">
         <f t="shared" si="7"/>
         <v>7</v>
       </c>
-      <c r="I13" s="52">
+      <c r="I13" s="64">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="J13" s="52">
+      <c r="J13" s="64">
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="K13" s="52">
+      <c r="K13" s="64">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="L13" s="52">
+      <c r="L13" s="64">
         <f t="shared" si="11"/>
         <v>11</v>
       </c>
-      <c r="M13" s="52">
+      <c r="M13" s="64">
         <f t="shared" si="12"/>
         <v>12</v>
       </c>
-      <c r="N13" s="52">
+      <c r="N13" s="64">
         <f t="shared" si="13"/>
         <v>13</v>
       </c>
-      <c r="O13" s="52">
+      <c r="O13" s="72">
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:15">
-      <c r="A14" s="53">
+      <c r="A14" s="65">
         <v>0.11</v>
       </c>
-      <c r="B14" s="54">
+      <c r="B14" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C14" s="54">
+      <c r="C14" s="66">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D14" s="54">
+      <c r="D14" s="66">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="66">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F14" s="54">
+      <c r="F14" s="66">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G14" s="54">
+      <c r="G14" s="66">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="H14" s="54">
+      <c r="H14" s="66">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="I14" s="54">
+      <c r="I14" s="66">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
-      <c r="J14" s="54">
+      <c r="J14" s="66">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="K14" s="54">
+      <c r="K14" s="66">
         <f t="shared" si="10"/>
         <v>11</v>
       </c>
-      <c r="L14" s="54">
+      <c r="L14" s="66">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
-      <c r="M14" s="54">
+      <c r="M14" s="66">
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
-      <c r="N14" s="54">
+      <c r="N14" s="66">
         <f t="shared" si="13"/>
         <v>14</v>
       </c>
-      <c r="O14" s="54">
+      <c r="O14" s="73">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:15">
-      <c r="A15" s="55">
+      <c r="A15" s="67">
         <v>0.12</v>
       </c>
-      <c r="B15" s="52">
+      <c r="B15" s="64">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C15" s="52">
+      <c r="C15" s="64">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E15" s="52">
+      <c r="E15" s="64">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F15" s="52">
+      <c r="F15" s="64">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="64">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="H15" s="52">
+      <c r="H15" s="64">
         <f t="shared" si="7"/>
         <v>8</v>
       </c>
-      <c r="I15" s="52">
+      <c r="I15" s="64">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="J15" s="52">
+      <c r="J15" s="64">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
-      <c r="K15" s="52">
+      <c r="K15" s="64">
         <f t="shared" si="10"/>
         <v>12</v>
       </c>
-      <c r="L15" s="52">
+      <c r="L15" s="64">
         <f t="shared" si="11"/>
         <v>13</v>
       </c>
-      <c r="M15" s="52">
+      <c r="M15" s="64">
         <f t="shared" si="12"/>
         <v>14</v>
       </c>
-      <c r="N15" s="52">
+      <c r="N15" s="64">
         <f t="shared" si="13"/>
         <v>16</v>
       </c>
-      <c r="O15" s="52">
+      <c r="O15" s="72">
         <f t="shared" si="14"/>
         <v>17</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:15">
-      <c r="A16" s="53">
+      <c r="A16" s="65">
         <v>0.13</v>
       </c>
-      <c r="B16" s="54">
+      <c r="B16" s="66">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C16" s="54">
+      <c r="C16" s="66">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D16" s="54">
+      <c r="D16" s="66">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E16" s="54">
+      <c r="E16" s="66">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="F16" s="54">
+      <c r="F16" s="66">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="G16" s="54">
+      <c r="G16" s="66">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="H16" s="54">
+      <c r="H16" s="66">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="I16" s="54">
+      <c r="I16" s="66">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="J16" s="54">
+      <c r="J16" s="66">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="K16" s="54">
+      <c r="K16" s="66">
         <f t="shared" si="10"/>
         <v>13</v>
       </c>
-      <c r="L16" s="54">
+      <c r="L16" s="66">
         <f t="shared" si="11"/>
         <v>14</v>
       </c>
-      <c r="M16" s="54">
+      <c r="M16" s="66">
         <f t="shared" si="12"/>
         <v>16</v>
       </c>
-      <c r="N16" s="54">
+      <c r="N16" s="66">
         <f t="shared" si="13"/>
         <v>17</v>
       </c>
-      <c r="O16" s="54">
+      <c r="O16" s="73">
         <f t="shared" si="14"/>
         <v>18</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:15">
-      <c r="A17" s="55">
+      <c r="A17" s="67">
         <v>0.14</v>
       </c>
-      <c r="B17" s="52">
+      <c r="B17" s="64">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="C17" s="52">
+      <c r="C17" s="64">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D17" s="52">
+      <c r="D17" s="64">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="E17" s="52">
+      <c r="E17" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F17" s="52">
+      <c r="F17" s="64">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="G17" s="52">
+      <c r="G17" s="64">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="H17" s="52">
+      <c r="H17" s="64">
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="I17" s="52">
+      <c r="I17" s="64">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="J17" s="52">
+      <c r="J17" s="64">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
-      <c r="K17" s="52">
+      <c r="K17" s="64">
         <f t="shared" si="10"/>
         <v>14</v>
       </c>
-      <c r="L17" s="52">
+      <c r="L17" s="64">
         <f t="shared" si="11"/>
         <v>15</v>
       </c>
-      <c r="M17" s="52">
+      <c r="M17" s="64">
         <f t="shared" si="12"/>
         <v>17</v>
       </c>
-      <c r="N17" s="52">
+      <c r="N17" s="64">
         <f t="shared" si="13"/>
         <v>18</v>
       </c>
-      <c r="O17" s="52">
+      <c r="O17" s="72">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:15">
-      <c r="A18" s="53">
+      <c r="A18" s="65">
         <v>0.15</v>
       </c>
-      <c r="B18" s="54">
+      <c r="B18" s="66">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C18" s="54">
+      <c r="C18" s="66">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D18" s="54">
+      <c r="D18" s="66">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="66">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F18" s="54">
+      <c r="F18" s="66">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="G18" s="54">
+      <c r="G18" s="66">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="H18" s="54">
+      <c r="H18" s="66">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="I18" s="54">
+      <c r="I18" s="66">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
-      <c r="J18" s="54">
+      <c r="J18" s="66">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="K18" s="54">
+      <c r="K18" s="66">
         <f t="shared" si="10"/>
         <v>15</v>
       </c>
-      <c r="L18" s="54">
+      <c r="L18" s="66">
         <f t="shared" si="11"/>
         <v>17</v>
       </c>
-      <c r="M18" s="54">
+      <c r="M18" s="66">
         <f t="shared" si="12"/>
         <v>18</v>
       </c>
-      <c r="N18" s="54">
+      <c r="N18" s="66">
         <f t="shared" si="13"/>
         <v>20</v>
       </c>
-      <c r="O18" s="54">
+      <c r="O18" s="73">
         <f t="shared" si="14"/>
         <v>21</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:15">
-      <c r="A19" s="55">
+      <c r="A19" s="67">
         <v>0.16</v>
       </c>
-      <c r="B19" s="52">
+      <c r="B19" s="64">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C19" s="52">
+      <c r="C19" s="64">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="64">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="64">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="64">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="H19" s="52">
+      <c r="H19" s="64">
         <f t="shared" si="7"/>
         <v>11</v>
       </c>
-      <c r="I19" s="52">
+      <c r="I19" s="64">
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
-      <c r="J19" s="52">
+      <c r="J19" s="64">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="K19" s="52">
+      <c r="K19" s="64">
         <f t="shared" si="10"/>
         <v>16</v>
       </c>
-      <c r="L19" s="52">
+      <c r="L19" s="64">
         <f t="shared" si="11"/>
         <v>18</v>
       </c>
-      <c r="M19" s="52">
+      <c r="M19" s="64">
         <f t="shared" si="12"/>
         <v>19</v>
       </c>
-      <c r="N19" s="52">
+      <c r="N19" s="64">
         <f t="shared" si="13"/>
         <v>21</v>
       </c>
-      <c r="O19" s="52">
+      <c r="O19" s="72">
         <f t="shared" si="14"/>
         <v>22</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:15">
-      <c r="A20" s="53">
+      <c r="A20" s="65">
         <v>0.17</v>
       </c>
-      <c r="B20" s="54">
+      <c r="B20" s="66">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C20" s="54">
+      <c r="C20" s="66">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="66">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="66">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="66">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="66">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="H20" s="54">
+      <c r="H20" s="66">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="I20" s="54">
+      <c r="I20" s="66">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="J20" s="54">
+      <c r="J20" s="66">
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="K20" s="54">
+      <c r="K20" s="66">
         <f t="shared" si="10"/>
         <v>17</v>
       </c>
-      <c r="L20" s="54">
+      <c r="L20" s="66">
         <f t="shared" si="11"/>
         <v>19</v>
       </c>
-      <c r="M20" s="54">
+      <c r="M20" s="66">
         <f t="shared" si="12"/>
         <v>20</v>
       </c>
-      <c r="N20" s="54">
+      <c r="N20" s="66">
         <f t="shared" si="13"/>
         <v>22</v>
       </c>
-      <c r="O20" s="54">
+      <c r="O20" s="73">
         <f t="shared" si="14"/>
         <v>24</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:15">
-      <c r="A21" s="55">
+      <c r="A21" s="67">
         <v>0.18</v>
       </c>
-      <c r="B21" s="52">
+      <c r="B21" s="64">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C21" s="52">
+      <c r="C21" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="64">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="E21" s="52">
+      <c r="E21" s="64">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="F21" s="52">
+      <c r="F21" s="64">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="G21" s="52">
+      <c r="G21" s="64">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="H21" s="52">
+      <c r="H21" s="64">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="I21" s="52">
+      <c r="I21" s="64">
         <f t="shared" si="8"/>
         <v>14</v>
       </c>
-      <c r="J21" s="52">
+      <c r="J21" s="64">
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="K21" s="52">
+      <c r="K21" s="64">
         <f t="shared" si="10"/>
         <v>18</v>
       </c>
-      <c r="L21" s="52">
+      <c r="L21" s="64">
         <f t="shared" si="11"/>
         <v>20</v>
       </c>
-      <c r="M21" s="52">
+      <c r="M21" s="64">
         <f t="shared" si="12"/>
         <v>22</v>
       </c>
-      <c r="N21" s="52">
+      <c r="N21" s="64">
         <f t="shared" si="13"/>
         <v>23</v>
       </c>
-      <c r="O21" s="52">
+      <c r="O21" s="72">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:15">
-      <c r="A22" s="53">
+      <c r="A22" s="65">
         <v>0.19</v>
       </c>
-      <c r="B22" s="54">
+      <c r="B22" s="66">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C22" s="54">
+      <c r="C22" s="66">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D22" s="54">
+      <c r="D22" s="66">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="E22" s="54">
+      <c r="E22" s="66">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F22" s="54">
+      <c r="F22" s="66">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="G22" s="54">
+      <c r="G22" s="66">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="H22" s="54">
+      <c r="H22" s="66">
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="I22" s="54">
+      <c r="I22" s="66">
         <f t="shared" si="8"/>
         <v>15</v>
       </c>
-      <c r="J22" s="54">
+      <c r="J22" s="66">
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="K22" s="54">
+      <c r="K22" s="66">
         <f t="shared" si="10"/>
         <v>19</v>
       </c>
-      <c r="L22" s="54">
+      <c r="L22" s="66">
         <f t="shared" si="11"/>
         <v>21</v>
       </c>
-      <c r="M22" s="54">
+      <c r="M22" s="66">
         <f t="shared" si="12"/>
         <v>23</v>
       </c>
-      <c r="N22" s="54">
+      <c r="N22" s="66">
         <f t="shared" si="13"/>
         <v>25</v>
       </c>
-      <c r="O22" s="54">
+      <c r="O22" s="73">
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:15">
-      <c r="A23" s="55">
+      <c r="A23" s="67">
         <v>0.2</v>
       </c>
-      <c r="B23" s="52">
+      <c r="B23" s="64">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C23" s="52">
+      <c r="C23" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="64">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="E23" s="52">
+      <c r="E23" s="64">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F23" s="52">
+      <c r="F23" s="64">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="G23" s="52">
+      <c r="G23" s="64">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
-      <c r="H23" s="52">
+      <c r="H23" s="64">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="I23" s="52">
+      <c r="I23" s="64">
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="J23" s="52">
+      <c r="J23" s="64">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="K23" s="52">
+      <c r="K23" s="64">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="L23" s="52">
+      <c r="L23" s="64">
         <f t="shared" si="11"/>
         <v>22</v>
       </c>
-      <c r="M23" s="52">
+      <c r="M23" s="64">
         <f t="shared" si="12"/>
         <v>24</v>
       </c>
-      <c r="N23" s="52">
+      <c r="N23" s="64">
         <f t="shared" si="13"/>
         <v>26</v>
       </c>
-      <c r="O23" s="52">
+      <c r="O23" s="72">
         <f t="shared" si="14"/>
         <v>28</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:15">
-      <c r="A24" s="53">
+      <c r="A24" s="65">
         <v>0.21</v>
       </c>
-      <c r="B24" s="54">
+      <c r="B24" s="66">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C24" s="54">
+      <c r="C24" s="66">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D24" s="54">
+      <c r="D24" s="66">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="E24" s="54">
+      <c r="E24" s="66">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="F24" s="54">
+      <c r="F24" s="66">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="G24" s="54">
+      <c r="G24" s="66">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="H24" s="54">
+      <c r="H24" s="66">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="I24" s="54">
+      <c r="I24" s="66">
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="J24" s="54">
+      <c r="J24" s="66">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="K24" s="54">
+      <c r="K24" s="66">
         <f t="shared" si="10"/>
         <v>21</v>
       </c>
-      <c r="L24" s="54">
+      <c r="L24" s="66">
         <f t="shared" si="11"/>
         <v>23</v>
       </c>
-      <c r="M24" s="54">
+      <c r="M24" s="66">
         <f t="shared" si="12"/>
         <v>25</v>
       </c>
-      <c r="N24" s="54">
+      <c r="N24" s="66">
         <f t="shared" si="13"/>
         <v>27</v>
       </c>
-      <c r="O24" s="54">
+      <c r="O24" s="73">
         <f t="shared" si="14"/>
         <v>29</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:15">
-      <c r="A25" s="55">
+      <c r="A25" s="67">
         <v>0.22</v>
       </c>
-      <c r="B25" s="52">
+      <c r="B25" s="64">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C25" s="52">
+      <c r="C25" s="64">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D25" s="52">
+      <c r="D25" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E25" s="52">
+      <c r="E25" s="64">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="F25" s="52">
+      <c r="F25" s="64">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="G25" s="52">
+      <c r="G25" s="64">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
-      <c r="H25" s="52">
+      <c r="H25" s="64">
         <f t="shared" si="7"/>
         <v>15</v>
       </c>
-      <c r="I25" s="52">
+      <c r="I25" s="64">
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="J25" s="52">
+      <c r="J25" s="64">
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="K25" s="52">
+      <c r="K25" s="64">
         <f t="shared" si="10"/>
         <v>22</v>
       </c>
-      <c r="L25" s="52">
+      <c r="L25" s="64">
         <f t="shared" si="11"/>
         <v>24</v>
       </c>
-      <c r="M25" s="52">
+      <c r="M25" s="64">
         <f t="shared" si="12"/>
         <v>26</v>
       </c>
-      <c r="N25" s="52">
+      <c r="N25" s="64">
         <f t="shared" si="13"/>
         <v>29</v>
       </c>
-      <c r="O25" s="52">
+      <c r="O25" s="72">
         <f t="shared" si="14"/>
         <v>31</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:15">
-      <c r="A26" s="53">
+      <c r="A26" s="65">
         <v>0.23</v>
       </c>
-      <c r="B26" s="54">
+      <c r="B26" s="66">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C26" s="54">
+      <c r="C26" s="66">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D26" s="54">
+      <c r="D26" s="66">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E26" s="54">
+      <c r="E26" s="66">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="F26" s="54">
+      <c r="F26" s="66">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="G26" s="54">
+      <c r="G26" s="66">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="H26" s="54">
+      <c r="H26" s="66">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
-      <c r="I26" s="54">
+      <c r="I26" s="66">
         <f t="shared" si="8"/>
         <v>18</v>
       </c>
-      <c r="J26" s="54">
+      <c r="J26" s="66">
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="K26" s="54">
+      <c r="K26" s="66">
         <f t="shared" si="10"/>
         <v>23</v>
       </c>
-      <c r="L26" s="54">
+      <c r="L26" s="66">
         <f t="shared" si="11"/>
         <v>25</v>
       </c>
-      <c r="M26" s="54">
+      <c r="M26" s="66">
         <f t="shared" si="12"/>
         <v>28</v>
       </c>
-      <c r="N26" s="54">
+      <c r="N26" s="66">
         <f t="shared" si="13"/>
         <v>30</v>
       </c>
-      <c r="O26" s="54">
+      <c r="O26" s="73">
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:15">
-      <c r="A27" s="55">
+      <c r="A27" s="67">
         <v>0.24</v>
       </c>
-      <c r="B27" s="52">
+      <c r="B27" s="64">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C27" s="52">
+      <c r="C27" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D27" s="52">
+      <c r="D27" s="64">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="E27" s="52">
+      <c r="E27" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F27" s="52">
+      <c r="F27" s="64">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="G27" s="52">
+      <c r="G27" s="64">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="H27" s="52">
+      <c r="H27" s="64">
         <f t="shared" si="7"/>
         <v>17</v>
       </c>
-      <c r="I27" s="52">
+      <c r="I27" s="64">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
-      <c r="J27" s="52">
+      <c r="J27" s="64">
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="K27" s="52">
+      <c r="K27" s="64">
         <f t="shared" si="10"/>
         <v>24</v>
       </c>
-      <c r="L27" s="52">
+      <c r="L27" s="64">
         <f t="shared" si="11"/>
         <v>26</v>
       </c>
-      <c r="M27" s="52">
+      <c r="M27" s="64">
         <f t="shared" si="12"/>
         <v>29</v>
       </c>
-      <c r="N27" s="52">
+      <c r="N27" s="64">
         <f t="shared" si="13"/>
         <v>31</v>
       </c>
-      <c r="O27" s="52">
+      <c r="O27" s="72">
         <f t="shared" si="14"/>
         <v>34</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:15">
-      <c r="A28" s="53">
+      <c r="A28" s="65">
         <v>0.25</v>
       </c>
-      <c r="B28" s="54">
+      <c r="B28" s="66">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C28" s="54">
+      <c r="C28" s="66">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D28" s="54">
+      <c r="D28" s="66">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="66">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F28" s="54">
+      <c r="F28" s="66">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="G28" s="54">
+      <c r="G28" s="66">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="H28" s="54">
+      <c r="H28" s="66">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="I28" s="54">
+      <c r="I28" s="66">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="J28" s="54">
+      <c r="J28" s="66">
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="K28" s="54">
+      <c r="K28" s="66">
         <f t="shared" si="10"/>
         <v>25</v>
       </c>
-      <c r="L28" s="54">
+      <c r="L28" s="66">
         <f t="shared" si="11"/>
         <v>28</v>
       </c>
-      <c r="M28" s="54">
+      <c r="M28" s="66">
         <f t="shared" si="12"/>
         <v>30</v>
       </c>
-      <c r="N28" s="54">
+      <c r="N28" s="66">
         <f t="shared" si="13"/>
         <v>33</v>
       </c>
-      <c r="O28" s="54">
+      <c r="O28" s="73">
         <f t="shared" si="14"/>
         <v>35</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:15">
-      <c r="A29" s="55">
+      <c r="A29" s="67">
         <v>0.26</v>
       </c>
-      <c r="B29" s="52">
+      <c r="B29" s="64">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C29" s="52">
+      <c r="C29" s="64">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D29" s="52">
+      <c r="D29" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E29" s="52">
+      <c r="E29" s="64">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="F29" s="52">
+      <c r="F29" s="64">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="G29" s="52">
+      <c r="G29" s="64">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="H29" s="52">
+      <c r="H29" s="64">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
-      <c r="I29" s="52">
+      <c r="I29" s="64">
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="J29" s="52">
+      <c r="J29" s="64">
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="K29" s="52">
+      <c r="K29" s="64">
         <f t="shared" si="10"/>
         <v>26</v>
       </c>
-      <c r="L29" s="52">
+      <c r="L29" s="64">
         <f t="shared" si="11"/>
         <v>29</v>
       </c>
-      <c r="M29" s="52">
+      <c r="M29" s="64">
         <f t="shared" si="12"/>
         <v>31</v>
       </c>
-      <c r="N29" s="52">
+      <c r="N29" s="64">
         <f t="shared" si="13"/>
         <v>34</v>
       </c>
-      <c r="O29" s="52">
+      <c r="O29" s="72">
         <f t="shared" si="14"/>
         <v>36</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:15">
-      <c r="A30" s="53">
+      <c r="A30" s="65">
         <v>0.27</v>
       </c>
-      <c r="B30" s="54">
+      <c r="B30" s="66">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C30" s="54">
+      <c r="C30" s="66">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="D30" s="54">
+      <c r="D30" s="66">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E30" s="54">
+      <c r="E30" s="66">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="F30" s="54">
+      <c r="F30" s="66">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="G30" s="54">
+      <c r="G30" s="66">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="H30" s="54">
+      <c r="H30" s="66">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
-      <c r="I30" s="54">
+      <c r="I30" s="66">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="J30" s="54">
+      <c r="J30" s="66">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="K30" s="54">
+      <c r="K30" s="66">
         <f t="shared" si="10"/>
         <v>27</v>
       </c>
-      <c r="L30" s="54">
+      <c r="L30" s="66">
         <f t="shared" si="11"/>
         <v>30</v>
       </c>
-      <c r="M30" s="54">
+      <c r="M30" s="66">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="N30" s="54">
+      <c r="N30" s="66">
         <f t="shared" si="13"/>
         <v>35</v>
       </c>
-      <c r="O30" s="54">
+      <c r="O30" s="73">
         <f t="shared" si="14"/>
         <v>38</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:15">
-      <c r="A31" s="55">
+      <c r="A31" s="67">
         <v>0.28</v>
       </c>
-      <c r="B31" s="52">
+      <c r="B31" s="64">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C31" s="52">
+      <c r="C31" s="64">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D31" s="52">
+      <c r="D31" s="64">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="E31" s="52">
+      <c r="E31" s="64">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="F31" s="52">
+      <c r="F31" s="64">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="G31" s="52">
+      <c r="G31" s="64">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="H31" s="52">
+      <c r="H31" s="64">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="I31" s="52">
+      <c r="I31" s="64">
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="J31" s="52">
+      <c r="J31" s="64">
         <f t="shared" si="9"/>
         <v>25</v>
       </c>
-      <c r="K31" s="52">
+      <c r="K31" s="64">
         <f t="shared" si="10"/>
         <v>28</v>
       </c>
-      <c r="L31" s="52">
+      <c r="L31" s="64">
         <f t="shared" si="11"/>
         <v>31</v>
       </c>
-      <c r="M31" s="52">
+      <c r="M31" s="64">
         <f t="shared" si="12"/>
         <v>34</v>
       </c>
-      <c r="N31" s="52">
+      <c r="N31" s="64">
         <f t="shared" si="13"/>
         <v>36</v>
       </c>
-      <c r="O31" s="52">
+      <c r="O31" s="72">
         <f t="shared" si="14"/>
         <v>39</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:15">
-      <c r="A32" s="53">
+      <c r="A32" s="65">
         <v>0.29</v>
       </c>
-      <c r="B32" s="54">
+      <c r="B32" s="66">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C32" s="54">
+      <c r="C32" s="66">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D32" s="54">
+      <c r="D32" s="66">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="E32" s="54">
+      <c r="E32" s="66">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="F32" s="54">
+      <c r="F32" s="66">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="G32" s="54">
+      <c r="G32" s="66">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
-      <c r="H32" s="54">
+      <c r="H32" s="66">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="I32" s="54">
+      <c r="I32" s="66">
         <f t="shared" si="8"/>
         <v>23</v>
       </c>
-      <c r="J32" s="54">
+      <c r="J32" s="66">
         <f t="shared" si="9"/>
         <v>26</v>
       </c>
-      <c r="K32" s="54">
+      <c r="K32" s="66">
         <f t="shared" si="10"/>
         <v>29</v>
       </c>
-      <c r="L32" s="54">
+      <c r="L32" s="66">
         <f t="shared" si="11"/>
         <v>32</v>
       </c>
-      <c r="M32" s="54">
+      <c r="M32" s="66">
         <f t="shared" si="12"/>
         <v>35</v>
       </c>
-      <c r="N32" s="54">
+      <c r="N32" s="66">
         <f t="shared" si="13"/>
         <v>38</v>
       </c>
-      <c r="O32" s="54">
+      <c r="O32" s="73">
         <f t="shared" si="14"/>
         <v>41</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:15">
-      <c r="A33" s="55">
+      <c r="A33" s="68">
         <v>0.3</v>
       </c>
-      <c r="B33" s="52">
+      <c r="B33" s="69">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C33" s="52">
+      <c r="C33" s="69">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="D33" s="52">
+      <c r="D33" s="69">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="E33" s="52">
+      <c r="E33" s="69">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="F33" s="52">
+      <c r="F33" s="69">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="G33" s="52">
+      <c r="G33" s="69">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
-      <c r="H33" s="52">
+      <c r="H33" s="69">
         <f t="shared" si="7"/>
         <v>21</v>
       </c>
-      <c r="I33" s="52">
+      <c r="I33" s="69">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="J33" s="52">
+      <c r="J33" s="69">
         <f t="shared" si="9"/>
         <v>27</v>
       </c>
-      <c r="K33" s="52">
+      <c r="K33" s="69">
         <f t="shared" si="10"/>
         <v>30</v>
       </c>
-      <c r="L33" s="52">
+      <c r="L33" s="69">
         <f t="shared" si="11"/>
         <v>33</v>
       </c>
-      <c r="M33" s="52">
+      <c r="M33" s="69">
         <f t="shared" si="12"/>
         <v>36</v>
       </c>
-      <c r="N33" s="52">
+      <c r="N33" s="69">
         <f t="shared" si="13"/>
         <v>39</v>
       </c>
-      <c r="O33" s="52">
+      <c r="O33" s="74">
         <f t="shared" si="14"/>
         <v>42</v>
       </c>
@@ -8005,7 +8247,7 @@
     <mergeCell ref="W1:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="50" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
     <ignoredError sqref="Q3" numberStoredAsText="1"/>
@@ -8015,8 +8257,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B37"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" customHeight="1" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="39.625" style="38" customWidth="1"/>
@@ -8076,6 +8320,10 @@
         <v>-0.03</v>
       </c>
     </row>
+    <row r="8" customHeight="1" spans="1:2">
+      <c r="A8" s="44"/>
+      <c r="B8" s="45"/>
+    </row>
     <row r="9" customHeight="1" spans="1:2">
       <c r="A9" s="41" t="s">
         <v>139</v>
@@ -8084,6 +8332,10 @@
         <v>140</v>
       </c>
     </row>
+    <row r="10" customHeight="1" spans="1:2">
+      <c r="A10" s="44"/>
+      <c r="B10" s="45"/>
+    </row>
     <row r="11" customHeight="1" spans="1:2">
       <c r="A11" s="41" t="s">
         <v>141</v>
@@ -8102,7 +8354,7 @@
     </row>
     <row r="13" customHeight="1" spans="1:2">
       <c r="A13" s="41"/>
-      <c r="B13" s="44"/>
+      <c r="B13" s="46"/>
     </row>
     <row r="14" customHeight="1" spans="1:2">
       <c r="A14" s="41" t="s">
@@ -8114,7 +8366,7 @@
     </row>
     <row r="15" customHeight="1" spans="1:2">
       <c r="A15" s="41"/>
-      <c r="B15" s="44"/>
+      <c r="B15" s="46"/>
     </row>
     <row r="16" customHeight="1" spans="1:2">
       <c r="A16" s="41" t="s">
@@ -8126,7 +8378,7 @@
     </row>
     <row r="17" customHeight="1" spans="1:2">
       <c r="A17" s="41"/>
-      <c r="B17" s="44"/>
+      <c r="B17" s="46"/>
     </row>
     <row r="18" customHeight="1" spans="1:2">
       <c r="A18" s="41" t="s">
@@ -8146,7 +8398,7 @@
     </row>
     <row r="20" customHeight="1" spans="1:2">
       <c r="A20" s="41"/>
-      <c r="B20" s="44"/>
+      <c r="B20" s="46"/>
     </row>
     <row r="21" customHeight="1" spans="1:2">
       <c r="A21" s="41" t="s">
@@ -8193,31 +8445,27 @@
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:2">
-      <c r="A27" s="41"/>
-      <c r="B27" s="44"/>
+      <c r="A27" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="28" customHeight="1" spans="1:2">
-      <c r="A28" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="B28" s="42" t="s">
-        <v>135</v>
-      </c>
+      <c r="A28" s="49"/>
+      <c r="B28" s="50"/>
     </row>
     <row r="29" customHeight="1" spans="1:2">
-      <c r="A29" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="B29" s="42" t="s">
-        <v>133</v>
-      </c>
+      <c r="A29" s="41"/>
+      <c r="B29" s="46"/>
     </row>
     <row r="30" customHeight="1" spans="1:2">
       <c r="A30" s="41" t="s">
         <v>158</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:2">
@@ -8229,49 +8477,79 @@
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:2">
-      <c r="A32" s="45" t="s">
+      <c r="A32" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="B32" s="45"/>
-    </row>
-    <row r="33" customHeight="1" spans="1:1">
-      <c r="A33" s="38" t="s">
+      <c r="B32" s="42" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:1">
-      <c r="A34" s="38" t="s">
+    <row r="33" customHeight="1" spans="1:2">
+      <c r="A33" s="41" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:1">
-      <c r="A35" s="38" t="s">
+      <c r="B33" s="42" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:1">
-      <c r="A36" s="38" t="s">
+    <row r="34" customHeight="1" spans="1:2">
+      <c r="A34" s="51" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:1">
-      <c r="A37" s="38" t="s">
+      <c r="B34" s="52"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:2">
+      <c r="A35" s="53" t="s">
         <v>165</v>
       </c>
+      <c r="B35" s="53"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:2">
+      <c r="A36" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" s="53"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:2">
+      <c r="A37" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="B37" s="53"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:2">
+      <c r="A38" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" s="53"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:2">
+      <c r="A39" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" s="53"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:2">
+      <c r="A40" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
+  <mergeCells count="9">
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B26:B31 B11:B24 B2:B4 B6:B9" numberStoredAsText="1"/>
+    <ignoredError sqref="B29:B31 B11:B24 B2:B4 B6:B9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8297,13 +8575,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="H1" s="25" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8321,132 +8599,132 @@
         <v>9</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:8">
       <c r="A3" s="24" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:8">
       <c r="A4" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>170</v>
-      </c>
       <c r="C4" s="26" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:8">
       <c r="A5" s="24" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E5" s="28"/>
       <c r="H5" s="25" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:8">
       <c r="A6" s="24" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C6" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>183</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>178</v>
       </c>
       <c r="E6" s="28"/>
       <c r="H6" s="25" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:8">
       <c r="A7" s="24" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C7" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>183</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>178</v>
       </c>
       <c r="E7" s="28"/>
       <c r="H7" s="25" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:5">
       <c r="A8" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="27" t="s">
         <v>187</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>182</v>
-      </c>
       <c r="D8" s="27" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:5">
       <c r="A9" s="24" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E9" s="28"/>
     </row>
@@ -8455,7 +8733,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -8478,63 +8756,63 @@
     </row>
     <row r="13" ht="15.75" spans="1:5">
       <c r="A13" s="24" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:5">
       <c r="A14" s="24" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E14" s="28"/>
     </row>
     <row r="15" ht="15.75" spans="1:5">
       <c r="A15" s="24" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C15" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="27" t="s">
         <v>183</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>178</v>
       </c>
       <c r="E15" s="28"/>
     </row>
     <row r="16" ht="15.75" spans="1:5">
       <c r="A16" s="29" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E16" s="30"/>
     </row>
@@ -8547,21 +8825,21 @@
     </row>
     <row r="18" ht="15.75" spans="1:4">
       <c r="A18" s="33" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B18" s="34"/>
       <c r="D18" s="34"/>
     </row>
     <row r="19" ht="15.75" spans="1:4">
       <c r="A19" s="35" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B19" s="34"/>
       <c r="D19" s="34"/>
     </row>
     <row r="20" ht="15.75" spans="1:1">
       <c r="A20" s="36" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -8575,7 +8853,7 @@
     <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -8592,112 +8870,112 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:6">
       <c r="A2" s="5"/>
       <c r="B2" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F2" s="4"/>
     </row>
     <row r="3" customHeight="1" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:5">
@@ -8709,23 +8987,23 @@
     </row>
     <row r="8" customHeight="1" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F8" s="12"/>
     </row>
     <row r="9" customHeight="1" spans="1:6">
       <c r="A9" s="13" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B9" s="14">
         <v>2</v>
@@ -8741,7 +9019,7 @@
     </row>
     <row r="10" customHeight="1" spans="1:6">
       <c r="A10" s="13" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B10" s="14">
         <v>1.5</v>
@@ -8757,7 +9035,7 @@
     </row>
     <row r="11" customHeight="1" spans="1:6">
       <c r="A11" s="13" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B11" s="14">
         <v>1</v>
@@ -8773,7 +9051,7 @@
     </row>
     <row r="12" customHeight="1" spans="1:6">
       <c r="A12" s="16" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B12" s="17">
         <v>0.5</v>
